--- a/docs/specs/StatusReportBI_2026.xlsx
+++ b/docs/specs/StatusReportBI_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diogofaria/Documents/Azure-NHB/nhb-project-delivery/docs/specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ED62B1-ADA4-AC4E-8F46-F8E08E944C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D29C40-7F16-754F-A646-C650B136F5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="246">
   <si>
     <t>Project ID</t>
   </si>
@@ -1836,620 +1836,6 @@
   <dxfs count="121">
     <dxf>
       <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3962,6 +3348,620 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4105,128 +4105,128 @@
     <tableColumn id="3" xr3:uid="{63642D60-CB02-45D4-BF90-C551A73005E7}" name="Status Projeto" dataDxfId="116"/>
     <tableColumn id="4" xr3:uid="{E95A609A-A81B-45BC-B3B9-07FFCB208FAF}" name="Responsável pelo Envio" dataDxfId="115" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{95099C14-44CF-4DF9-B110-9C242326F4CA}" name="Semana 1" dataDxfId="114" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{73414AEB-ABC1-4A6A-9CFA-6ED9C059DCAF}" name="Semana 2" dataDxfId="27" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{122FFB43-8DB4-4E9E-B22F-D7ADC7687ECE}" name="Semana 3" dataDxfId="26" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{1E7C0653-A3EF-4816-957A-20E6F2B21AF2}" name="Semana 4" dataDxfId="25" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{1154A540-4FCB-4780-8A79-F70769F72D06}" name="Semana 5" dataDxfId="24" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{95D5B214-2B54-4364-8368-63D22D61234F}" name="Semana 6" dataDxfId="23" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{65D198C8-B714-4D67-8CD9-20B9A69B14A8}" name="Semana 7" dataDxfId="22" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{9F8773A6-C0B8-46FB-A9A5-F8C7663AAB72}" name="Semana 8" dataDxfId="21" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{DB086BC0-A2E6-4B72-9E18-0A2773B3BDEC}" name="Semana 9" dataDxfId="20" dataCellStyle="Normal"/>
-    <tableColumn id="14" xr3:uid="{03482946-921A-489E-9B6E-13A09D34521F}" name="Semana 10" dataDxfId="19" dataCellStyle="Normal"/>
-    <tableColumn id="15" xr3:uid="{36E37EF5-1859-4D70-A226-00032CDBE725}" name="Semana 11" dataDxfId="18" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{EA28C418-2D0C-4407-8DEA-6BED9D1F13CD}" name="Semana 12" dataDxfId="17" dataCellStyle="Normal"/>
-    <tableColumn id="17" xr3:uid="{03E48B39-D02B-4107-AC9B-850BF98D70F1}" name="Semana 13" dataDxfId="16" dataCellStyle="Normal"/>
-    <tableColumn id="18" xr3:uid="{3016A65B-31F8-4B15-AEEF-74725A05E045}" name="Semana 14" dataDxfId="15" dataCellStyle="Normal"/>
-    <tableColumn id="19" xr3:uid="{0148934D-5053-41B7-A64C-6ECEE770522E}" name="Semana 15" dataDxfId="14" dataCellStyle="Normal"/>
-    <tableColumn id="20" xr3:uid="{9DE17A1F-203B-4603-B5B8-0F73840A571D}" name="Semana 16" dataDxfId="13" dataCellStyle="Normal"/>
-    <tableColumn id="21" xr3:uid="{4967A8CE-8AFC-4D25-82EB-3306AF40FA4D}" name="Semana 17" dataDxfId="12" dataCellStyle="Normal"/>
-    <tableColumn id="22" xr3:uid="{F5338EA1-8715-4EB8-8099-1305BB6C982A}" name="Semana 18" dataDxfId="11" dataCellStyle="Normal"/>
-    <tableColumn id="23" xr3:uid="{495CA1A8-9DB6-4D29-BBED-C2E6348B3CE4}" name="Semana 19" dataDxfId="10" dataCellStyle="Normal"/>
-    <tableColumn id="24" xr3:uid="{E7125378-96DB-4D78-85E8-5C7C30485827}" name="Semana 20" dataDxfId="9" dataCellStyle="Normal"/>
-    <tableColumn id="25" xr3:uid="{3A40A1FA-9A58-48F2-9956-BD8778E33B35}" name="Semana 21" dataDxfId="8" dataCellStyle="Normal"/>
-    <tableColumn id="26" xr3:uid="{CC488376-5634-40F7-A570-73F74BCC52C9}" name="Semana 22" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="27" xr3:uid="{3C318C5C-FEDD-45B7-AB98-52F9865ED23F}" name="Semana 23" dataDxfId="6" dataCellStyle="Normal"/>
-    <tableColumn id="28" xr3:uid="{0AAEB85E-2EBA-4F3D-9DA5-F641D0795AD5}" name="Semana 24" dataDxfId="5" dataCellStyle="Normal"/>
-    <tableColumn id="29" xr3:uid="{15A3A05F-39E6-4114-8E21-8948D6D215B6}" name="Semana 25" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="30" xr3:uid="{82ED50ED-A64E-4DE7-8234-E87F8E1EF798}" name="Semana 26" dataDxfId="3" dataCellStyle="Normal"/>
-    <tableColumn id="31" xr3:uid="{BAF65312-CFFF-44AE-9138-5D3A6D27E7C7}" name="Semana 27" dataDxfId="2" dataCellStyle="Normal"/>
-    <tableColumn id="32" xr3:uid="{A740F5FB-84C5-4A56-9A8D-D7992F2DF04D}" name="Semana 28" dataDxfId="1" dataCellStyle="Normal"/>
-    <tableColumn id="33" xr3:uid="{B574E1B2-4909-4AD3-9F06-4B1258242DB3}" name="Semana 29" dataDxfId="0" dataCellStyle="Normal"/>
-    <tableColumn id="34" xr3:uid="{6B841F49-49FD-4D60-B298-ACACAFE16783}" name="Semana 30" dataDxfId="113" dataCellStyle="Normal"/>
-    <tableColumn id="35" xr3:uid="{7775AB51-894F-451C-8868-0EA34C0DEF51}" name="Semana 31" dataDxfId="112" dataCellStyle="Normal"/>
-    <tableColumn id="36" xr3:uid="{D7E75888-0F8F-4BF3-AADA-273C4A0C85F4}" name="Semana 32" dataDxfId="111" dataCellStyle="Normal"/>
-    <tableColumn id="37" xr3:uid="{45AD0369-8FF4-45E2-9A72-A52C5CA873E3}" name="Semana 33" dataDxfId="110" dataCellStyle="Normal"/>
-    <tableColumn id="38" xr3:uid="{C5F33218-0780-4982-B1BD-C98114844466}" name="Semana 34" dataDxfId="109" dataCellStyle="Normal"/>
-    <tableColumn id="39" xr3:uid="{9A87502B-AB25-4DEE-A852-2EB6CB627ED5}" name="Semana 35" dataDxfId="108" dataCellStyle="Normal"/>
-    <tableColumn id="40" xr3:uid="{43993064-1F0B-42B0-8910-20411F7D5206}" name="Semana 36" dataDxfId="107" dataCellStyle="Normal"/>
-    <tableColumn id="41" xr3:uid="{8FA42040-EE3D-4B55-9FCF-94904F31B067}" name="Semana 37" dataDxfId="106" dataCellStyle="Normal"/>
-    <tableColumn id="42" xr3:uid="{BF992F4E-A115-475B-895A-1D33CFA3B5AE}" name="Semana 38" dataDxfId="105" dataCellStyle="Normal"/>
-    <tableColumn id="43" xr3:uid="{094398BA-73C4-4D4E-B5C5-B732C46BB5AC}" name="Semana 39" dataDxfId="104" dataCellStyle="Normal"/>
-    <tableColumn id="44" xr3:uid="{093D68FD-B45A-4175-A81E-1802F10A5F2B}" name="Semana 40" dataDxfId="103" dataCellStyle="Normal"/>
-    <tableColumn id="45" xr3:uid="{EF9413F4-133C-4D71-9376-15B16CF6D450}" name="Semana 41" dataDxfId="102" dataCellStyle="Normal"/>
-    <tableColumn id="46" xr3:uid="{ED936B61-8F48-49B8-B05F-D81645FCAFFA}" name="Semana 42" dataDxfId="101" dataCellStyle="Normal"/>
-    <tableColumn id="47" xr3:uid="{27CBDBAC-4916-406F-8E7E-0A96CE34203C}" name="Semana 43" dataDxfId="100" dataCellStyle="Normal"/>
-    <tableColumn id="48" xr3:uid="{BC1B5741-A3D0-4F2E-9514-221D71F4D87D}" name="Semana 44" dataDxfId="99" dataCellStyle="Normal"/>
-    <tableColumn id="49" xr3:uid="{3F463363-3716-4230-B5F9-A8425BB1BBFD}" name="Semana 45" dataDxfId="98" dataCellStyle="Normal"/>
-    <tableColumn id="50" xr3:uid="{B21BE339-C896-4291-925E-91832D88BD3B}" name="Semana 46" dataDxfId="97" dataCellStyle="Normal"/>
-    <tableColumn id="51" xr3:uid="{4978273D-36B6-40A4-9E59-57BECD4F31CC}" name="Semana 47" dataDxfId="96" dataCellStyle="Normal"/>
-    <tableColumn id="52" xr3:uid="{BE0BD3B9-6E97-48B1-8FF2-EEE0915D3137}" name="Semana 48" dataDxfId="95" dataCellStyle="Normal"/>
-    <tableColumn id="53" xr3:uid="{FED24952-113C-4790-993E-3B5172B319B2}" name="Semana 49" dataDxfId="94" dataCellStyle="Normal"/>
-    <tableColumn id="54" xr3:uid="{FF8CD072-9365-498B-9E7E-2CBDF528A19B}" name="Semana 50" dataDxfId="93" dataCellStyle="Normal"/>
-    <tableColumn id="55" xr3:uid="{A9D5CE35-E74A-4CD9-BA33-ECA5C406AB38}" name="Semana 51" dataDxfId="92" dataCellStyle="Normal"/>
-    <tableColumn id="56" xr3:uid="{C086F1D6-06DB-46AF-9DDF-4E460E8BD8E0}" name="Semana 52" dataDxfId="91" dataCellStyle="Normal"/>
-    <tableColumn id="57" xr3:uid="{C942B3B3-E3B6-4201-82B8-5641A2709F68}" name="Total de Status nas Semanas" dataDxfId="90" dataCellStyle="Normal"/>
-    <tableColumn id="58" xr3:uid="{4EEC2AEC-C5B4-460B-A06F-F44BA640360A}" name="Total de status não enviados" dataDxfId="89" dataCellStyle="Normal"/>
-    <tableColumn id="59" xr3:uid="{F27A72D0-C6D2-4CAE-8C97-0F94070EA169}" name="Total que deveria ter sido enviado" dataDxfId="88" dataCellStyle="Normal"/>
-    <tableColumn id="60" xr3:uid="{F935478D-2905-48CF-88A8-01F8D0043E04}" name="OBS" dataDxfId="87" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{73414AEB-ABC1-4A6A-9CFA-6ED9C059DCAF}" name="Semana 2" dataDxfId="113" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{122FFB43-8DB4-4E9E-B22F-D7ADC7687ECE}" name="Semana 3" dataDxfId="112" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{1E7C0653-A3EF-4816-957A-20E6F2B21AF2}" name="Semana 4" dataDxfId="111" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{1154A540-4FCB-4780-8A79-F70769F72D06}" name="Semana 5" dataDxfId="110" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{95D5B214-2B54-4364-8368-63D22D61234F}" name="Semana 6" dataDxfId="109" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{65D198C8-B714-4D67-8CD9-20B9A69B14A8}" name="Semana 7" dataDxfId="108" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{9F8773A6-C0B8-46FB-A9A5-F8C7663AAB72}" name="Semana 8" dataDxfId="107" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{DB086BC0-A2E6-4B72-9E18-0A2773B3BDEC}" name="Semana 9" dataDxfId="106" dataCellStyle="Normal"/>
+    <tableColumn id="14" xr3:uid="{03482946-921A-489E-9B6E-13A09D34521F}" name="Semana 10" dataDxfId="105" dataCellStyle="Normal"/>
+    <tableColumn id="15" xr3:uid="{36E37EF5-1859-4D70-A226-00032CDBE725}" name="Semana 11" dataDxfId="104" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{EA28C418-2D0C-4407-8DEA-6BED9D1F13CD}" name="Semana 12" dataDxfId="103" dataCellStyle="Normal"/>
+    <tableColumn id="17" xr3:uid="{03E48B39-D02B-4107-AC9B-850BF98D70F1}" name="Semana 13" dataDxfId="102" dataCellStyle="Normal"/>
+    <tableColumn id="18" xr3:uid="{3016A65B-31F8-4B15-AEEF-74725A05E045}" name="Semana 14" dataDxfId="101" dataCellStyle="Normal"/>
+    <tableColumn id="19" xr3:uid="{0148934D-5053-41B7-A64C-6ECEE770522E}" name="Semana 15" dataDxfId="100" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{9DE17A1F-203B-4603-B5B8-0F73840A571D}" name="Semana 16" dataDxfId="99" dataCellStyle="Normal"/>
+    <tableColumn id="21" xr3:uid="{4967A8CE-8AFC-4D25-82EB-3306AF40FA4D}" name="Semana 17" dataDxfId="98" dataCellStyle="Normal"/>
+    <tableColumn id="22" xr3:uid="{F5338EA1-8715-4EB8-8099-1305BB6C982A}" name="Semana 18" dataDxfId="97" dataCellStyle="Normal"/>
+    <tableColumn id="23" xr3:uid="{495CA1A8-9DB6-4D29-BBED-C2E6348B3CE4}" name="Semana 19" dataDxfId="96" dataCellStyle="Normal"/>
+    <tableColumn id="24" xr3:uid="{E7125378-96DB-4D78-85E8-5C7C30485827}" name="Semana 20" dataDxfId="95" dataCellStyle="Normal"/>
+    <tableColumn id="25" xr3:uid="{3A40A1FA-9A58-48F2-9956-BD8778E33B35}" name="Semana 21" dataDxfId="94" dataCellStyle="Normal"/>
+    <tableColumn id="26" xr3:uid="{CC488376-5634-40F7-A570-73F74BCC52C9}" name="Semana 22" dataDxfId="93" dataCellStyle="Normal"/>
+    <tableColumn id="27" xr3:uid="{3C318C5C-FEDD-45B7-AB98-52F9865ED23F}" name="Semana 23" dataDxfId="92" dataCellStyle="Normal"/>
+    <tableColumn id="28" xr3:uid="{0AAEB85E-2EBA-4F3D-9DA5-F641D0795AD5}" name="Semana 24" dataDxfId="91" dataCellStyle="Normal"/>
+    <tableColumn id="29" xr3:uid="{15A3A05F-39E6-4114-8E21-8948D6D215B6}" name="Semana 25" dataDxfId="90" dataCellStyle="Normal"/>
+    <tableColumn id="30" xr3:uid="{82ED50ED-A64E-4DE7-8234-E87F8E1EF798}" name="Semana 26" dataDxfId="89" dataCellStyle="Normal"/>
+    <tableColumn id="31" xr3:uid="{BAF65312-CFFF-44AE-9138-5D3A6D27E7C7}" name="Semana 27" dataDxfId="88" dataCellStyle="Normal"/>
+    <tableColumn id="32" xr3:uid="{A740F5FB-84C5-4A56-9A8D-D7992F2DF04D}" name="Semana 28" dataDxfId="87" dataCellStyle="Normal"/>
+    <tableColumn id="33" xr3:uid="{B574E1B2-4909-4AD3-9F06-4B1258242DB3}" name="Semana 29" dataDxfId="86" dataCellStyle="Normal"/>
+    <tableColumn id="34" xr3:uid="{6B841F49-49FD-4D60-B298-ACACAFE16783}" name="Semana 30" dataDxfId="85" dataCellStyle="Normal"/>
+    <tableColumn id="35" xr3:uid="{7775AB51-894F-451C-8868-0EA34C0DEF51}" name="Semana 31" dataDxfId="84" dataCellStyle="Normal"/>
+    <tableColumn id="36" xr3:uid="{D7E75888-0F8F-4BF3-AADA-273C4A0C85F4}" name="Semana 32" dataDxfId="83" dataCellStyle="Normal"/>
+    <tableColumn id="37" xr3:uid="{45AD0369-8FF4-45E2-9A72-A52C5CA873E3}" name="Semana 33" dataDxfId="82" dataCellStyle="Normal"/>
+    <tableColumn id="38" xr3:uid="{C5F33218-0780-4982-B1BD-C98114844466}" name="Semana 34" dataDxfId="81" dataCellStyle="Normal"/>
+    <tableColumn id="39" xr3:uid="{9A87502B-AB25-4DEE-A852-2EB6CB627ED5}" name="Semana 35" dataDxfId="80" dataCellStyle="Normal"/>
+    <tableColumn id="40" xr3:uid="{43993064-1F0B-42B0-8910-20411F7D5206}" name="Semana 36" dataDxfId="79" dataCellStyle="Normal"/>
+    <tableColumn id="41" xr3:uid="{8FA42040-EE3D-4B55-9FCF-94904F31B067}" name="Semana 37" dataDxfId="78" dataCellStyle="Normal"/>
+    <tableColumn id="42" xr3:uid="{BF992F4E-A115-475B-895A-1D33CFA3B5AE}" name="Semana 38" dataDxfId="77" dataCellStyle="Normal"/>
+    <tableColumn id="43" xr3:uid="{094398BA-73C4-4D4E-B5C5-B732C46BB5AC}" name="Semana 39" dataDxfId="76" dataCellStyle="Normal"/>
+    <tableColumn id="44" xr3:uid="{093D68FD-B45A-4175-A81E-1802F10A5F2B}" name="Semana 40" dataDxfId="75" dataCellStyle="Normal"/>
+    <tableColumn id="45" xr3:uid="{EF9413F4-133C-4D71-9376-15B16CF6D450}" name="Semana 41" dataDxfId="74" dataCellStyle="Normal"/>
+    <tableColumn id="46" xr3:uid="{ED936B61-8F48-49B8-B05F-D81645FCAFFA}" name="Semana 42" dataDxfId="73" dataCellStyle="Normal"/>
+    <tableColumn id="47" xr3:uid="{27CBDBAC-4916-406F-8E7E-0A96CE34203C}" name="Semana 43" dataDxfId="72" dataCellStyle="Normal"/>
+    <tableColumn id="48" xr3:uid="{BC1B5741-A3D0-4F2E-9514-221D71F4D87D}" name="Semana 44" dataDxfId="71" dataCellStyle="Normal"/>
+    <tableColumn id="49" xr3:uid="{3F463363-3716-4230-B5F9-A8425BB1BBFD}" name="Semana 45" dataDxfId="70" dataCellStyle="Normal"/>
+    <tableColumn id="50" xr3:uid="{B21BE339-C896-4291-925E-91832D88BD3B}" name="Semana 46" dataDxfId="69" dataCellStyle="Normal"/>
+    <tableColumn id="51" xr3:uid="{4978273D-36B6-40A4-9E59-57BECD4F31CC}" name="Semana 47" dataDxfId="68" dataCellStyle="Normal"/>
+    <tableColumn id="52" xr3:uid="{BE0BD3B9-6E97-48B1-8FF2-EEE0915D3137}" name="Semana 48" dataDxfId="67" dataCellStyle="Normal"/>
+    <tableColumn id="53" xr3:uid="{FED24952-113C-4790-993E-3B5172B319B2}" name="Semana 49" dataDxfId="66" dataCellStyle="Normal"/>
+    <tableColumn id="54" xr3:uid="{FF8CD072-9365-498B-9E7E-2CBDF528A19B}" name="Semana 50" dataDxfId="65" dataCellStyle="Normal"/>
+    <tableColumn id="55" xr3:uid="{A9D5CE35-E74A-4CD9-BA33-ECA5C406AB38}" name="Semana 51" dataDxfId="64" dataCellStyle="Normal"/>
+    <tableColumn id="56" xr3:uid="{C086F1D6-06DB-46AF-9DDF-4E460E8BD8E0}" name="Semana 52" dataDxfId="63" dataCellStyle="Normal"/>
+    <tableColumn id="57" xr3:uid="{C942B3B3-E3B6-4201-82B8-5641A2709F68}" name="Total de Status nas Semanas" dataDxfId="62" dataCellStyle="Normal"/>
+    <tableColumn id="58" xr3:uid="{4EEC2AEC-C5B4-460B-A06F-F44BA640360A}" name="Total de status não enviados" dataDxfId="61" dataCellStyle="Normal"/>
+    <tableColumn id="59" xr3:uid="{F27A72D0-C6D2-4CAE-8C97-0F94070EA169}" name="Total que deveria ter sido enviado" dataDxfId="60" dataCellStyle="Normal"/>
+    <tableColumn id="60" xr3:uid="{F935478D-2905-48CF-88A8-01F8D0043E04}" name="OBS" dataDxfId="59" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81E4E6BB-0F5E-4E4D-9851-E6D3C097EB26}" name="tbl_StatusReport2" displayName="tbl_StatusReport2" ref="A1:BH43" totalsRowShown="0" headerRowDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81E4E6BB-0F5E-4E4D-9851-E6D3C097EB26}" name="tbl_StatusReport2" displayName="tbl_StatusReport2" ref="A1:BH43" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A1:BH43" xr:uid="{83E74578-6452-4198-8AF3-C0841F627FE0}"/>
   <tableColumns count="60">
     <tableColumn id="1" xr3:uid="{60644CF8-7FC5-47A9-8F97-C081DF7E0D50}" name="Project ID" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{C2AF5DF4-E408-4A0F-B0FF-D3F1D949D995}" name="Project Name" dataCellStyle="Normal"/>
     <tableColumn id="3" xr3:uid="{C40CFA33-177C-4A0E-B079-EFC40DAB6BC5}" name="Status Projeto" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{B067411B-105E-459A-A1F3-21C5FDF1CD52}" name="Resposnável pelo Envio" dataDxfId="85" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{B95BED59-99A7-436F-AC30-A28EBCCA6931}" name="Semana 1" dataDxfId="84" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{AA50DD29-3BD2-4412-B8CA-5D2D63F23E00}" name="Semana 2" dataDxfId="83" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{50862FA4-D291-4946-95C7-BF84D25DEDD2}" name="Semana 3" dataDxfId="82" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{7C2FAF54-DB38-4B15-875F-687B7CA3D9DB}" name="Semana 4" dataDxfId="81" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{E7FBD991-572B-437F-9490-CF7F73F2802B}" name="Semana 5" dataDxfId="80" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{ADEA988C-51D7-4E69-8A79-3B2240A433F1}" name="Semana 6" dataDxfId="79" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{77DB9460-2902-4E0A-B35B-A011DEA9E930}" name="Semana 7" dataDxfId="78" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{88504A38-4176-4622-8A62-7F35DAD02FD8}" name="Semana 8" dataDxfId="77" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{84A6395D-BC23-4C3D-B4DB-A2766FFFC887}" name="Semana 9" dataDxfId="76" dataCellStyle="Normal"/>
-    <tableColumn id="14" xr3:uid="{C615CFA6-862C-450D-8227-7B01CBA54D31}" name="Semana 10" dataDxfId="75" dataCellStyle="Normal"/>
-    <tableColumn id="15" xr3:uid="{B850C858-77F5-4FDA-B1B3-67E98753E073}" name="Semana 11" dataDxfId="74" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{5B024900-3FE2-427A-8C1F-EDE695A2F073}" name="Semana 12" dataDxfId="73" dataCellStyle="Normal"/>
-    <tableColumn id="17" xr3:uid="{7E1C5632-B6C3-4F84-B269-653123E54573}" name="Semana 13" dataDxfId="72" dataCellStyle="Normal"/>
-    <tableColumn id="18" xr3:uid="{FDE37690-441F-40CF-871D-D8E32B78AB65}" name="Semana 14" dataDxfId="71" dataCellStyle="Normal"/>
-    <tableColumn id="19" xr3:uid="{4B879AF5-BDD8-4CCE-BC4D-EEB14F5C4FE6}" name="Semana 15" dataDxfId="70" dataCellStyle="Normal"/>
-    <tableColumn id="20" xr3:uid="{88BF33A8-3F7E-4A07-A77D-DEC63A3E1509}" name="Semana 16" dataDxfId="69" dataCellStyle="Normal"/>
-    <tableColumn id="21" xr3:uid="{1403F70F-7A64-4AC8-8535-15D6D8BDB4B9}" name="Semana 17" dataDxfId="68" dataCellStyle="Normal"/>
-    <tableColumn id="22" xr3:uid="{ECD4A88B-FE92-44FC-B7B8-3B4051F3308E}" name="Semana 18" dataDxfId="67" dataCellStyle="Normal"/>
-    <tableColumn id="23" xr3:uid="{F786310B-6FBB-4243-A793-0F09B01CA51B}" name="Semana 19" dataDxfId="66" dataCellStyle="Normal"/>
-    <tableColumn id="24" xr3:uid="{3A82CE0E-C593-45FD-87A7-A10A2204BDD7}" name="Semana 20" dataDxfId="65" dataCellStyle="Normal"/>
-    <tableColumn id="25" xr3:uid="{68BFF4E4-666B-4869-9A5B-CDA95C7FCEC7}" name="Semana 21" dataDxfId="64" dataCellStyle="Normal"/>
-    <tableColumn id="26" xr3:uid="{0EBA6F0D-9236-4C6E-A272-5F35D0EC5AB1}" name="Semana 22" dataDxfId="63" dataCellStyle="Normal"/>
-    <tableColumn id="27" xr3:uid="{EA331F7A-2713-4B9A-8BE4-4D02293B94D1}" name="Semana 23" dataDxfId="62" dataCellStyle="Normal"/>
-    <tableColumn id="28" xr3:uid="{F9E988BA-9C7F-4DA2-A9E9-29D34ADA88B8}" name="Semana 24" dataDxfId="61" dataCellStyle="Normal"/>
-    <tableColumn id="29" xr3:uid="{FCB56C4C-13F5-4BC5-86B1-03980E2095E4}" name="Semana 25" dataDxfId="60" dataCellStyle="Normal"/>
-    <tableColumn id="30" xr3:uid="{8E849DFF-59E7-434F-889D-C41E8C12990E}" name="Semana 26" dataDxfId="59" dataCellStyle="Normal"/>
-    <tableColumn id="31" xr3:uid="{3E22461B-7491-4D06-9C1D-AA584C13527A}" name="Semana 27" dataDxfId="58" dataCellStyle="Normal"/>
-    <tableColumn id="32" xr3:uid="{9E8D9E17-F503-435F-9640-A9CE2F572BDB}" name="Semana 28" dataDxfId="57" dataCellStyle="Normal"/>
-    <tableColumn id="33" xr3:uid="{73E0A55D-D20F-4CE7-AA47-08846AD9334E}" name="Semana 29" dataDxfId="56" dataCellStyle="Normal"/>
-    <tableColumn id="34" xr3:uid="{347728D7-EE6E-4DB2-820D-EDEA42978F39}" name="Semana 30" dataDxfId="55" dataCellStyle="Normal"/>
-    <tableColumn id="35" xr3:uid="{44E5172E-706C-4C6F-B8EA-B3EC54F01EB0}" name="Semana 31" dataDxfId="54" dataCellStyle="Normal"/>
-    <tableColumn id="36" xr3:uid="{C842825A-9412-4AB0-830C-41A75F2B05E9}" name="Semana 32" dataDxfId="53" dataCellStyle="Normal"/>
-    <tableColumn id="37" xr3:uid="{9BE5AE3B-2B4F-48CE-B0D8-2CA714EBA5AA}" name="Semana 33" dataDxfId="52" dataCellStyle="Normal"/>
-    <tableColumn id="38" xr3:uid="{64947CDC-1740-43D0-BBC7-5DF40FE818DB}" name="Semana 34" dataDxfId="51" dataCellStyle="Normal"/>
-    <tableColumn id="39" xr3:uid="{6E9FFA5C-C002-4015-AC26-ADE6FD7BD69F}" name="Semana 35" dataDxfId="50" dataCellStyle="Normal"/>
-    <tableColumn id="40" xr3:uid="{8C851BDB-E328-41E3-8D67-B236D267C287}" name="Semana 36" dataDxfId="49" dataCellStyle="Normal"/>
-    <tableColumn id="41" xr3:uid="{E21EA4CD-8EDF-4B55-8961-16519034BD4E}" name="Semana 37" dataDxfId="48" dataCellStyle="Normal"/>
-    <tableColumn id="42" xr3:uid="{B6573B96-9C38-4F68-B9B8-682581FADBC6}" name="Semana 38" dataDxfId="47" dataCellStyle="Normal"/>
-    <tableColumn id="43" xr3:uid="{EB8E5AAE-406E-428F-8F43-E9CCC85E95B7}" name="Semana 39" dataDxfId="46" dataCellStyle="Normal"/>
-    <tableColumn id="44" xr3:uid="{12200613-60B9-40AC-982D-CB89B99C2521}" name="Semana 40" dataDxfId="45" dataCellStyle="Normal"/>
-    <tableColumn id="45" xr3:uid="{6C5EF691-5409-400E-B3FB-D2FE35FD9F60}" name="Semana 41" dataDxfId="44" dataCellStyle="Normal"/>
-    <tableColumn id="46" xr3:uid="{0DE71B90-7FB4-4EA4-B156-9F327948F5B3}" name="Semana 42" dataDxfId="43" dataCellStyle="Normal"/>
-    <tableColumn id="47" xr3:uid="{E80A05C4-33DB-4CDA-B5AC-9475DAA59C1D}" name="Semana 43" dataDxfId="42" dataCellStyle="Normal"/>
-    <tableColumn id="48" xr3:uid="{A13DC0AC-4020-4D91-88A2-A3CF5023D71E}" name="Semana 44" dataDxfId="41" dataCellStyle="Normal"/>
-    <tableColumn id="49" xr3:uid="{A129B4C7-FEA3-4455-876A-8598B5495606}" name="Semana 45" dataDxfId="40" dataCellStyle="Normal"/>
-    <tableColumn id="50" xr3:uid="{5E4DC677-E036-42BE-A97F-5DAB924E573D}" name="Semana 46" dataDxfId="39" dataCellStyle="Normal"/>
-    <tableColumn id="51" xr3:uid="{A67EE59D-51AB-40D8-9CE3-DB8524EC975F}" name="Semana 47" dataDxfId="38" dataCellStyle="Normal"/>
-    <tableColumn id="52" xr3:uid="{3A58EC60-C207-4911-81D8-91540AD1ED46}" name="Semana 48" dataDxfId="37" dataCellStyle="Normal"/>
-    <tableColumn id="53" xr3:uid="{40541B89-AE21-4406-B4FA-25E62DC9FA1B}" name="Semana 49" dataDxfId="36" dataCellStyle="Normal"/>
-    <tableColumn id="54" xr3:uid="{30EF9924-92E3-43A3-B133-E547C044E2E3}" name="Semana 50" dataDxfId="35" dataCellStyle="Normal"/>
-    <tableColumn id="55" xr3:uid="{9B7F822E-7A2C-4EE0-8027-D60A40614815}" name="Semana 51" dataDxfId="34" dataCellStyle="Normal"/>
-    <tableColumn id="56" xr3:uid="{B949C798-3D55-4A69-AB99-63103C551AB7}" name="Semana 52" dataDxfId="33" dataCellStyle="Normal"/>
-    <tableColumn id="57" xr3:uid="{6E7C401A-C5D4-4B4D-9497-9B2289A4E425}" name="Total de Status nas Semanas" dataDxfId="32" dataCellStyle="Normal"/>
-    <tableColumn id="58" xr3:uid="{6B89C980-EBAD-4DCE-BA8F-204316393746}" name="Total de status não enviados" dataDxfId="31" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{B067411B-105E-459A-A1F3-21C5FDF1CD52}" name="Resposnável pelo Envio" dataDxfId="57" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{B95BED59-99A7-436F-AC30-A28EBCCA6931}" name="Semana 1" dataDxfId="56" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{AA50DD29-3BD2-4412-B8CA-5D2D63F23E00}" name="Semana 2" dataDxfId="55" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{50862FA4-D291-4946-95C7-BF84D25DEDD2}" name="Semana 3" dataDxfId="54" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{7C2FAF54-DB38-4B15-875F-687B7CA3D9DB}" name="Semana 4" dataDxfId="53" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{E7FBD991-572B-437F-9490-CF7F73F2802B}" name="Semana 5" dataDxfId="52" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{ADEA988C-51D7-4E69-8A79-3B2240A433F1}" name="Semana 6" dataDxfId="51" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{77DB9460-2902-4E0A-B35B-A011DEA9E930}" name="Semana 7" dataDxfId="50" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{88504A38-4176-4622-8A62-7F35DAD02FD8}" name="Semana 8" dataDxfId="49" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{84A6395D-BC23-4C3D-B4DB-A2766FFFC887}" name="Semana 9" dataDxfId="48" dataCellStyle="Normal"/>
+    <tableColumn id="14" xr3:uid="{C615CFA6-862C-450D-8227-7B01CBA54D31}" name="Semana 10" dataDxfId="47" dataCellStyle="Normal"/>
+    <tableColumn id="15" xr3:uid="{B850C858-77F5-4FDA-B1B3-67E98753E073}" name="Semana 11" dataDxfId="46" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{5B024900-3FE2-427A-8C1F-EDE695A2F073}" name="Semana 12" dataDxfId="45" dataCellStyle="Normal"/>
+    <tableColumn id="17" xr3:uid="{7E1C5632-B6C3-4F84-B269-653123E54573}" name="Semana 13" dataDxfId="44" dataCellStyle="Normal"/>
+    <tableColumn id="18" xr3:uid="{FDE37690-441F-40CF-871D-D8E32B78AB65}" name="Semana 14" dataDxfId="43" dataCellStyle="Normal"/>
+    <tableColumn id="19" xr3:uid="{4B879AF5-BDD8-4CCE-BC4D-EEB14F5C4FE6}" name="Semana 15" dataDxfId="42" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{88BF33A8-3F7E-4A07-A77D-DEC63A3E1509}" name="Semana 16" dataDxfId="41" dataCellStyle="Normal"/>
+    <tableColumn id="21" xr3:uid="{1403F70F-7A64-4AC8-8535-15D6D8BDB4B9}" name="Semana 17" dataDxfId="40" dataCellStyle="Normal"/>
+    <tableColumn id="22" xr3:uid="{ECD4A88B-FE92-44FC-B7B8-3B4051F3308E}" name="Semana 18" dataDxfId="39" dataCellStyle="Normal"/>
+    <tableColumn id="23" xr3:uid="{F786310B-6FBB-4243-A793-0F09B01CA51B}" name="Semana 19" dataDxfId="38" dataCellStyle="Normal"/>
+    <tableColumn id="24" xr3:uid="{3A82CE0E-C593-45FD-87A7-A10A2204BDD7}" name="Semana 20" dataDxfId="37" dataCellStyle="Normal"/>
+    <tableColumn id="25" xr3:uid="{68BFF4E4-666B-4869-9A5B-CDA95C7FCEC7}" name="Semana 21" dataDxfId="36" dataCellStyle="Normal"/>
+    <tableColumn id="26" xr3:uid="{0EBA6F0D-9236-4C6E-A272-5F35D0EC5AB1}" name="Semana 22" dataDxfId="35" dataCellStyle="Normal"/>
+    <tableColumn id="27" xr3:uid="{EA331F7A-2713-4B9A-8BE4-4D02293B94D1}" name="Semana 23" dataDxfId="34" dataCellStyle="Normal"/>
+    <tableColumn id="28" xr3:uid="{F9E988BA-9C7F-4DA2-A9E9-29D34ADA88B8}" name="Semana 24" dataDxfId="33" dataCellStyle="Normal"/>
+    <tableColumn id="29" xr3:uid="{FCB56C4C-13F5-4BC5-86B1-03980E2095E4}" name="Semana 25" dataDxfId="32" dataCellStyle="Normal"/>
+    <tableColumn id="30" xr3:uid="{8E849DFF-59E7-434F-889D-C41E8C12990E}" name="Semana 26" dataDxfId="31" dataCellStyle="Normal"/>
+    <tableColumn id="31" xr3:uid="{3E22461B-7491-4D06-9C1D-AA584C13527A}" name="Semana 27" dataDxfId="30" dataCellStyle="Normal"/>
+    <tableColumn id="32" xr3:uid="{9E8D9E17-F503-435F-9640-A9CE2F572BDB}" name="Semana 28" dataDxfId="29" dataCellStyle="Normal"/>
+    <tableColumn id="33" xr3:uid="{73E0A55D-D20F-4CE7-AA47-08846AD9334E}" name="Semana 29" dataDxfId="28" dataCellStyle="Normal"/>
+    <tableColumn id="34" xr3:uid="{347728D7-EE6E-4DB2-820D-EDEA42978F39}" name="Semana 30" dataDxfId="27" dataCellStyle="Normal"/>
+    <tableColumn id="35" xr3:uid="{44E5172E-706C-4C6F-B8EA-B3EC54F01EB0}" name="Semana 31" dataDxfId="26" dataCellStyle="Normal"/>
+    <tableColumn id="36" xr3:uid="{C842825A-9412-4AB0-830C-41A75F2B05E9}" name="Semana 32" dataDxfId="25" dataCellStyle="Normal"/>
+    <tableColumn id="37" xr3:uid="{9BE5AE3B-2B4F-48CE-B0D8-2CA714EBA5AA}" name="Semana 33" dataDxfId="24" dataCellStyle="Normal"/>
+    <tableColumn id="38" xr3:uid="{64947CDC-1740-43D0-BBC7-5DF40FE818DB}" name="Semana 34" dataDxfId="23" dataCellStyle="Normal"/>
+    <tableColumn id="39" xr3:uid="{6E9FFA5C-C002-4015-AC26-ADE6FD7BD69F}" name="Semana 35" dataDxfId="22" dataCellStyle="Normal"/>
+    <tableColumn id="40" xr3:uid="{8C851BDB-E328-41E3-8D67-B236D267C287}" name="Semana 36" dataDxfId="21" dataCellStyle="Normal"/>
+    <tableColumn id="41" xr3:uid="{E21EA4CD-8EDF-4B55-8961-16519034BD4E}" name="Semana 37" dataDxfId="20" dataCellStyle="Normal"/>
+    <tableColumn id="42" xr3:uid="{B6573B96-9C38-4F68-B9B8-682581FADBC6}" name="Semana 38" dataDxfId="19" dataCellStyle="Normal"/>
+    <tableColumn id="43" xr3:uid="{EB8E5AAE-406E-428F-8F43-E9CCC85E95B7}" name="Semana 39" dataDxfId="18" dataCellStyle="Normal"/>
+    <tableColumn id="44" xr3:uid="{12200613-60B9-40AC-982D-CB89B99C2521}" name="Semana 40" dataDxfId="17" dataCellStyle="Normal"/>
+    <tableColumn id="45" xr3:uid="{6C5EF691-5409-400E-B3FB-D2FE35FD9F60}" name="Semana 41" dataDxfId="16" dataCellStyle="Normal"/>
+    <tableColumn id="46" xr3:uid="{0DE71B90-7FB4-4EA4-B156-9F327948F5B3}" name="Semana 42" dataDxfId="15" dataCellStyle="Normal"/>
+    <tableColumn id="47" xr3:uid="{E80A05C4-33DB-4CDA-B5AC-9475DAA59C1D}" name="Semana 43" dataDxfId="14" dataCellStyle="Normal"/>
+    <tableColumn id="48" xr3:uid="{A13DC0AC-4020-4D91-88A2-A3CF5023D71E}" name="Semana 44" dataDxfId="13" dataCellStyle="Normal"/>
+    <tableColumn id="49" xr3:uid="{A129B4C7-FEA3-4455-876A-8598B5495606}" name="Semana 45" dataDxfId="12" dataCellStyle="Normal"/>
+    <tableColumn id="50" xr3:uid="{5E4DC677-E036-42BE-A97F-5DAB924E573D}" name="Semana 46" dataDxfId="11" dataCellStyle="Normal"/>
+    <tableColumn id="51" xr3:uid="{A67EE59D-51AB-40D8-9CE3-DB8524EC975F}" name="Semana 47" dataDxfId="10" dataCellStyle="Normal"/>
+    <tableColumn id="52" xr3:uid="{3A58EC60-C207-4911-81D8-91540AD1ED46}" name="Semana 48" dataDxfId="9" dataCellStyle="Normal"/>
+    <tableColumn id="53" xr3:uid="{40541B89-AE21-4406-B4FA-25E62DC9FA1B}" name="Semana 49" dataDxfId="8" dataCellStyle="Normal"/>
+    <tableColumn id="54" xr3:uid="{30EF9924-92E3-43A3-B133-E547C044E2E3}" name="Semana 50" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="55" xr3:uid="{9B7F822E-7A2C-4EE0-8027-D60A40614815}" name="Semana 51" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="56" xr3:uid="{B949C798-3D55-4A69-AB99-63103C551AB7}" name="Semana 52" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="57" xr3:uid="{6E7C401A-C5D4-4B4D-9497-9B2289A4E425}" name="Total de Status nas Semanas" dataDxfId="4" dataCellStyle="Normal"/>
+    <tableColumn id="58" xr3:uid="{6B89C980-EBAD-4DCE-BA8F-204316393746}" name="Total de status não enviados" dataDxfId="3" dataCellStyle="Normal"/>
     <tableColumn id="59" xr3:uid="{97155E31-5C8F-48CC-A34F-9194D502D533}" name="Total que deveria ter sido enviado" dataCellStyle="Normal"/>
     <tableColumn id="60" xr3:uid="{63CBFB0A-8CCB-4273-AB4B-7AF1EABCA026}" name="OBS" dataCellStyle="Normal"/>
   </tableColumns>
@@ -4843,90 +4843,34 @@
       <c r="E2" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF2" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG2" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
       <c r="AH2" s="40"/>
       <c r="AI2" s="40"/>
       <c r="AJ2" s="40"/>
@@ -4978,90 +4922,34 @@
       <c r="E3" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG3" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="44"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="44"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="44"/>
       <c r="AH3" s="41"/>
       <c r="AI3" s="41"/>
       <c r="AJ3" s="41"/>
@@ -5108,90 +4996,34 @@
       <c r="E4" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG4" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
       <c r="AH4" s="41"/>
       <c r="AI4" s="41"/>
       <c r="AJ4" s="41"/>
@@ -5243,90 +5075,34 @@
       <c r="E5" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF5" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG5" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="44"/>
+      <c r="X5" s="44"/>
+      <c r="Y5" s="44"/>
+      <c r="Z5" s="44"/>
+      <c r="AA5" s="44"/>
+      <c r="AB5" s="44"/>
+      <c r="AC5" s="44"/>
+      <c r="AD5" s="44"/>
+      <c r="AE5" s="44"/>
+      <c r="AF5" s="44"/>
+      <c r="AG5" s="44"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
@@ -5378,90 +5154,34 @@
       <c r="E6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG6" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="44"/>
+      <c r="Z6" s="44"/>
+      <c r="AA6" s="44"/>
+      <c r="AB6" s="44"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="44"/>
+      <c r="AE6" s="44"/>
+      <c r="AF6" s="44"/>
+      <c r="AG6" s="44"/>
       <c r="AH6" s="41"/>
       <c r="AI6" s="41"/>
       <c r="AJ6" s="41"/>
@@ -5514,90 +5234,34 @@
       <c r="E7" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF7" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG7" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="44"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
       <c r="AH7" s="41"/>
       <c r="AI7" s="41"/>
       <c r="AJ7" s="41"/>
@@ -5649,90 +5313,34 @@
       <c r="E8" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG8" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="44"/>
+      <c r="AB8" s="44"/>
+      <c r="AC8" s="44"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="44"/>
+      <c r="AF8" s="44"/>
+      <c r="AG8" s="44"/>
       <c r="AH8" s="41"/>
       <c r="AI8" s="41"/>
       <c r="AJ8" s="41"/>
@@ -5784,90 +5392,34 @@
       <c r="E9" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF9" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG9" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
       <c r="AH9" s="41"/>
       <c r="AI9" s="41"/>
       <c r="AJ9" s="41"/>
@@ -5919,90 +5471,34 @@
       <c r="E10" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF10" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG10" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="44"/>
+      <c r="AF10" s="44"/>
+      <c r="AG10" s="44"/>
       <c r="AH10" s="41"/>
       <c r="AI10" s="41"/>
       <c r="AJ10" s="41"/>
@@ -6054,90 +5550,34 @@
       <c r="E11" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF11" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG11" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
+      <c r="AG11" s="44"/>
       <c r="AH11" s="41"/>
       <c r="AI11" s="41"/>
       <c r="AJ11" s="41"/>
@@ -6189,90 +5629,34 @@
       <c r="E12" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG12" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="44"/>
+      <c r="AB12" s="44"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="44"/>
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="44"/>
       <c r="AH12" s="41"/>
       <c r="AI12" s="41"/>
       <c r="AJ12" s="41"/>
@@ -6324,90 +5708,34 @@
       <c r="E13" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF13" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG13" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="44"/>
+      <c r="Y13" s="44"/>
+      <c r="Z13" s="44"/>
+      <c r="AA13" s="44"/>
+      <c r="AB13" s="44"/>
+      <c r="AC13" s="44"/>
+      <c r="AD13" s="44"/>
+      <c r="AE13" s="44"/>
+      <c r="AF13" s="44"/>
+      <c r="AG13" s="44"/>
       <c r="AH13" s="41"/>
       <c r="AI13" s="41"/>
       <c r="AJ13" s="41"/>
@@ -6459,90 +5787,34 @@
       <c r="E14" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF14" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG14" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="44"/>
+      <c r="X14" s="44"/>
+      <c r="Y14" s="44"/>
+      <c r="Z14" s="44"/>
+      <c r="AA14" s="44"/>
+      <c r="AB14" s="44"/>
+      <c r="AC14" s="44"/>
+      <c r="AD14" s="44"/>
+      <c r="AE14" s="44"/>
+      <c r="AF14" s="44"/>
+      <c r="AG14" s="44"/>
       <c r="AH14" s="41"/>
       <c r="AI14" s="41"/>
       <c r="AJ14" s="41"/>
@@ -6594,90 +5866,34 @@
       <c r="E15" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF15" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG15" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="44"/>
+      <c r="AB15" s="44"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="44"/>
+      <c r="AE15" s="44"/>
+      <c r="AF15" s="44"/>
+      <c r="AG15" s="44"/>
       <c r="AH15" s="41"/>
       <c r="AI15" s="41"/>
       <c r="AJ15" s="41"/>
@@ -6729,90 +5945,34 @@
       <c r="E16" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF16" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG16" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44"/>
+      <c r="Z16" s="44"/>
+      <c r="AA16" s="44"/>
+      <c r="AB16" s="44"/>
+      <c r="AC16" s="44"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="44"/>
+      <c r="AF16" s="44"/>
+      <c r="AG16" s="44"/>
       <c r="AH16" s="41"/>
       <c r="AI16" s="41"/>
       <c r="AJ16" s="41"/>
@@ -6864,90 +6024,34 @@
       <c r="E17" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF17" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG17" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="44"/>
+      <c r="X17" s="44"/>
+      <c r="Y17" s="44"/>
+      <c r="Z17" s="44"/>
+      <c r="AA17" s="44"/>
+      <c r="AB17" s="44"/>
+      <c r="AC17" s="44"/>
+      <c r="AD17" s="44"/>
+      <c r="AE17" s="44"/>
+      <c r="AF17" s="44"/>
+      <c r="AG17" s="44"/>
       <c r="AH17" s="41"/>
       <c r="AI17" s="41"/>
       <c r="AJ17" s="41"/>
@@ -7001,90 +6105,34 @@
       <c r="E18" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF18" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG18" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="44"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="44"/>
+      <c r="Z18" s="44"/>
+      <c r="AA18" s="44"/>
+      <c r="AB18" s="44"/>
+      <c r="AC18" s="44"/>
+      <c r="AD18" s="44"/>
+      <c r="AE18" s="44"/>
+      <c r="AF18" s="44"/>
+      <c r="AG18" s="44"/>
       <c r="AH18" s="41"/>
       <c r="AI18" s="41"/>
       <c r="AJ18" s="41"/>
@@ -7136,90 +6184,34 @@
       <c r="E19" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF19" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG19" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="44"/>
+      <c r="X19" s="44"/>
+      <c r="Y19" s="44"/>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="44"/>
+      <c r="AB19" s="44"/>
+      <c r="AC19" s="44"/>
+      <c r="AD19" s="44"/>
+      <c r="AE19" s="44"/>
+      <c r="AF19" s="44"/>
+      <c r="AG19" s="44"/>
       <c r="AH19" s="41"/>
       <c r="AI19" s="41"/>
       <c r="AJ19" s="41"/>
@@ -7271,90 +6263,34 @@
       <c r="E20" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG20" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="44"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="44"/>
+      <c r="X20" s="44"/>
+      <c r="Y20" s="44"/>
+      <c r="Z20" s="44"/>
+      <c r="AA20" s="44"/>
+      <c r="AB20" s="44"/>
+      <c r="AC20" s="44"/>
+      <c r="AD20" s="44"/>
+      <c r="AE20" s="44"/>
+      <c r="AF20" s="44"/>
+      <c r="AG20" s="44"/>
       <c r="AH20" s="41"/>
       <c r="AI20" s="41"/>
       <c r="AJ20" s="41"/>
@@ -7406,90 +6342,34 @@
       <c r="E21" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF21" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG21" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="44"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="44"/>
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="44"/>
+      <c r="AB21" s="44"/>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="44"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="44"/>
       <c r="AH21" s="41"/>
       <c r="AI21" s="41"/>
       <c r="AJ21" s="41"/>
@@ -7542,90 +6422,34 @@
       <c r="E22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF22" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG22" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="44"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="44"/>
+      <c r="AB22" s="44"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="44"/>
+      <c r="AE22" s="44"/>
+      <c r="AF22" s="44"/>
+      <c r="AG22" s="44"/>
       <c r="AH22" s="41"/>
       <c r="AI22" s="41"/>
       <c r="AJ22" s="41"/>
@@ -7679,90 +6503,34 @@
       <c r="E23" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG23" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="44"/>
+      <c r="X23" s="44"/>
+      <c r="Y23" s="44"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="44"/>
+      <c r="AB23" s="44"/>
+      <c r="AC23" s="44"/>
+      <c r="AD23" s="44"/>
+      <c r="AE23" s="44"/>
+      <c r="AF23" s="44"/>
+      <c r="AG23" s="44"/>
       <c r="AH23" s="41"/>
       <c r="AI23" s="41"/>
       <c r="AJ23" s="41"/>
@@ -7814,90 +6582,34 @@
       <c r="E24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF24" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG24" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="44"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="44"/>
+      <c r="Z24" s="44"/>
+      <c r="AA24" s="44"/>
+      <c r="AB24" s="44"/>
+      <c r="AC24" s="44"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="44"/>
+      <c r="AF24" s="44"/>
+      <c r="AG24" s="44"/>
       <c r="AH24" s="41"/>
       <c r="AI24" s="41"/>
       <c r="AJ24" s="41"/>
@@ -7949,90 +6661,34 @@
       <c r="E25" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG25" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="44"/>
+      <c r="W25" s="44"/>
+      <c r="X25" s="44"/>
+      <c r="Y25" s="44"/>
+      <c r="Z25" s="44"/>
+      <c r="AA25" s="44"/>
+      <c r="AB25" s="44"/>
+      <c r="AC25" s="44"/>
+      <c r="AD25" s="44"/>
+      <c r="AE25" s="44"/>
+      <c r="AF25" s="44"/>
+      <c r="AG25" s="44"/>
       <c r="AH25" s="41"/>
       <c r="AI25" s="41"/>
       <c r="AJ25" s="41"/>
@@ -8084,90 +6740,34 @@
       <c r="E26" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF26" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG26" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="44"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="44"/>
+      <c r="Y26" s="44"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="44"/>
+      <c r="AB26" s="44"/>
+      <c r="AC26" s="44"/>
+      <c r="AD26" s="44"/>
+      <c r="AE26" s="44"/>
+      <c r="AF26" s="44"/>
+      <c r="AG26" s="44"/>
       <c r="AH26" s="41"/>
       <c r="AI26" s="41"/>
       <c r="AJ26" s="41"/>
@@ -8219,90 +6819,34 @@
       <c r="E27" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF27" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG27" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="44"/>
+      <c r="X27" s="44"/>
+      <c r="Y27" s="44"/>
+      <c r="Z27" s="44"/>
+      <c r="AA27" s="44"/>
+      <c r="AB27" s="44"/>
+      <c r="AC27" s="44"/>
+      <c r="AD27" s="44"/>
+      <c r="AE27" s="44"/>
+      <c r="AF27" s="44"/>
+      <c r="AG27" s="44"/>
       <c r="AH27" s="41"/>
       <c r="AI27" s="41"/>
       <c r="AJ27" s="41"/>
@@ -8354,90 +6898,34 @@
       <c r="E28" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF28" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG28" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="44"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="44"/>
+      <c r="X28" s="44"/>
+      <c r="Y28" s="44"/>
+      <c r="Z28" s="44"/>
+      <c r="AA28" s="44"/>
+      <c r="AB28" s="44"/>
+      <c r="AC28" s="44"/>
+      <c r="AD28" s="44"/>
+      <c r="AE28" s="44"/>
+      <c r="AF28" s="44"/>
+      <c r="AG28" s="44"/>
       <c r="AH28" s="41"/>
       <c r="AI28" s="41"/>
       <c r="AJ28" s="41"/>
@@ -8489,90 +6977,34 @@
       <c r="E29" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF29" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG29" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="44"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="44"/>
+      <c r="X29" s="44"/>
+      <c r="Y29" s="44"/>
+      <c r="Z29" s="44"/>
+      <c r="AA29" s="44"/>
+      <c r="AB29" s="44"/>
+      <c r="AC29" s="44"/>
+      <c r="AD29" s="44"/>
+      <c r="AE29" s="44"/>
+      <c r="AF29" s="44"/>
+      <c r="AG29" s="44"/>
       <c r="AH29" s="41"/>
       <c r="AI29" s="41"/>
       <c r="AJ29" s="41"/>
@@ -8624,90 +7056,34 @@
       <c r="E30" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF30" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG30" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="44"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="44"/>
+      <c r="AB30" s="44"/>
+      <c r="AC30" s="44"/>
+      <c r="AD30" s="44"/>
+      <c r="AE30" s="44"/>
+      <c r="AF30" s="44"/>
+      <c r="AG30" s="44"/>
       <c r="AH30" s="41"/>
       <c r="AI30" s="41"/>
       <c r="AJ30" s="41"/>
@@ -8757,90 +7133,34 @@
       <c r="E31" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF31" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG31" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="44"/>
+      <c r="Y31" s="44"/>
+      <c r="Z31" s="44"/>
+      <c r="AA31" s="44"/>
+      <c r="AB31" s="44"/>
+      <c r="AC31" s="44"/>
+      <c r="AD31" s="44"/>
+      <c r="AE31" s="44"/>
+      <c r="AF31" s="44"/>
+      <c r="AG31" s="44"/>
       <c r="AH31" s="41"/>
       <c r="AI31" s="41"/>
       <c r="AJ31" s="41"/>
@@ -8892,90 +7212,34 @@
       <c r="E32" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF32" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG32" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="44"/>
+      <c r="AB32" s="44"/>
+      <c r="AC32" s="44"/>
+      <c r="AD32" s="44"/>
+      <c r="AE32" s="44"/>
+      <c r="AF32" s="44"/>
+      <c r="AG32" s="44"/>
       <c r="AH32" s="41"/>
       <c r="AI32" s="41"/>
       <c r="AJ32" s="41"/>
@@ -9027,90 +7291,34 @@
       <c r="E33" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF33" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG33" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="44"/>
+      <c r="AB33" s="44"/>
+      <c r="AC33" s="44"/>
+      <c r="AD33" s="44"/>
+      <c r="AE33" s="44"/>
+      <c r="AF33" s="44"/>
+      <c r="AG33" s="44"/>
       <c r="AH33" s="41"/>
       <c r="AI33" s="41"/>
       <c r="AJ33" s="41"/>
@@ -9163,90 +7371,34 @@
       <c r="E34" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF34" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG34" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="44"/>
+      <c r="Y34" s="44"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="44"/>
+      <c r="AB34" s="44"/>
+      <c r="AC34" s="44"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="44"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="44"/>
       <c r="AH34" s="41"/>
       <c r="AI34" s="41"/>
       <c r="AJ34" s="41"/>
@@ -9298,90 +7450,34 @@
       <c r="E35" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF35" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG35" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="44"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="44"/>
+      <c r="X35" s="44"/>
+      <c r="Y35" s="44"/>
+      <c r="Z35" s="44"/>
+      <c r="AA35" s="44"/>
+      <c r="AB35" s="44"/>
+      <c r="AC35" s="44"/>
+      <c r="AD35" s="44"/>
+      <c r="AE35" s="44"/>
+      <c r="AF35" s="44"/>
+      <c r="AG35" s="44"/>
       <c r="AH35" s="41"/>
       <c r="AI35" s="41"/>
       <c r="AJ35" s="41"/>
@@ -9433,90 +7529,34 @@
       <c r="E36" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF36" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG36" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="44"/>
+      <c r="P36" s="44"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="44"/>
+      <c r="S36" s="44"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="44"/>
+      <c r="V36" s="44"/>
+      <c r="W36" s="44"/>
+      <c r="X36" s="44"/>
+      <c r="Y36" s="44"/>
+      <c r="Z36" s="44"/>
+      <c r="AA36" s="44"/>
+      <c r="AB36" s="44"/>
+      <c r="AC36" s="44"/>
+      <c r="AD36" s="44"/>
+      <c r="AE36" s="44"/>
+      <c r="AF36" s="44"/>
+      <c r="AG36" s="44"/>
       <c r="AH36" s="41"/>
       <c r="AI36" s="41"/>
       <c r="AJ36" s="41"/>
@@ -9568,90 +7608,34 @@
       <c r="E37" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF37" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG37" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44"/>
+      <c r="P37" s="44"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="44"/>
+      <c r="S37" s="44"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="44"/>
+      <c r="V37" s="44"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="44"/>
+      <c r="AB37" s="44"/>
+      <c r="AC37" s="44"/>
+      <c r="AD37" s="44"/>
+      <c r="AE37" s="44"/>
+      <c r="AF37" s="44"/>
+      <c r="AG37" s="44"/>
       <c r="AH37" s="41"/>
       <c r="AI37" s="41"/>
       <c r="AJ37" s="41"/>
@@ -9703,90 +7687,34 @@
       <c r="E38" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG38" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="44"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="44"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="44"/>
+      <c r="AC38" s="44"/>
+      <c r="AD38" s="44"/>
+      <c r="AE38" s="44"/>
+      <c r="AF38" s="44"/>
+      <c r="AG38" s="44"/>
       <c r="AH38" s="41"/>
       <c r="AI38" s="41"/>
       <c r="AJ38" s="41"/>
@@ -9840,90 +7768,34 @@
       <c r="E39" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF39" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG39" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="44"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="44"/>
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="44"/>
+      <c r="AB39" s="44"/>
+      <c r="AC39" s="44"/>
+      <c r="AD39" s="44"/>
+      <c r="AE39" s="44"/>
+      <c r="AF39" s="44"/>
+      <c r="AG39" s="44"/>
       <c r="AH39" s="41"/>
       <c r="AI39" s="41"/>
       <c r="AJ39" s="41"/>
@@ -9975,90 +7847,34 @@
       <c r="E40" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF40" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG40" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="44"/>
+      <c r="P40" s="44"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="44"/>
+      <c r="AB40" s="44"/>
+      <c r="AC40" s="44"/>
+      <c r="AD40" s="44"/>
+      <c r="AE40" s="44"/>
+      <c r="AF40" s="44"/>
+      <c r="AG40" s="44"/>
       <c r="AH40" s="41"/>
       <c r="AI40" s="41"/>
       <c r="AJ40" s="41"/>
@@ -10110,90 +7926,34 @@
       <c r="E41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF41" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG41" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="44"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="44"/>
+      <c r="AA41" s="44"/>
+      <c r="AB41" s="44"/>
+      <c r="AC41" s="44"/>
+      <c r="AD41" s="44"/>
+      <c r="AE41" s="44"/>
+      <c r="AF41" s="44"/>
+      <c r="AG41" s="44"/>
       <c r="AH41" s="41"/>
       <c r="AI41" s="41"/>
       <c r="AJ41" s="41"/>
@@ -10245,90 +8005,34 @@
       <c r="E42" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF42" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG42" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="44"/>
+      <c r="M42" s="44"/>
+      <c r="N42" s="44"/>
+      <c r="O42" s="44"/>
+      <c r="P42" s="44"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="44"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="44"/>
+      <c r="X42" s="44"/>
+      <c r="Y42" s="44"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="44"/>
+      <c r="AB42" s="44"/>
+      <c r="AC42" s="44"/>
+      <c r="AD42" s="44"/>
+      <c r="AE42" s="44"/>
+      <c r="AF42" s="44"/>
+      <c r="AG42" s="44"/>
       <c r="AH42" s="4"/>
       <c r="AI42" s="4"/>
       <c r="AJ42" s="4"/>
@@ -10380,90 +8084,34 @@
       <c r="E43" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF43" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG43" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="44"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="44"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="44"/>
+      <c r="W43" s="44"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="44"/>
+      <c r="AB43" s="44"/>
+      <c r="AC43" s="44"/>
+      <c r="AD43" s="44"/>
+      <c r="AE43" s="44"/>
+      <c r="AF43" s="44"/>
+      <c r="AG43" s="44"/>
       <c r="AH43" s="4"/>
       <c r="AI43" s="4"/>
       <c r="AJ43" s="4"/>
@@ -10515,90 +8163,34 @@
       <c r="E44" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF44" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG44" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="44"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="44"/>
+      <c r="P44" s="44"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="44"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="44"/>
+      <c r="V44" s="44"/>
+      <c r="W44" s="44"/>
+      <c r="X44" s="44"/>
+      <c r="Y44" s="44"/>
+      <c r="Z44" s="44"/>
+      <c r="AA44" s="44"/>
+      <c r="AB44" s="44"/>
+      <c r="AC44" s="44"/>
+      <c r="AD44" s="44"/>
+      <c r="AE44" s="44"/>
+      <c r="AF44" s="44"/>
+      <c r="AG44" s="44"/>
       <c r="AH44" s="4"/>
       <c r="AI44" s="4"/>
       <c r="AJ44" s="4"/>
@@ -10644,90 +8236,34 @@
       <c r="E45" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF45" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG45" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
+      <c r="O45" s="44"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="44"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="44"/>
+      <c r="AC45" s="44"/>
+      <c r="AD45" s="44"/>
+      <c r="AE45" s="44"/>
+      <c r="AF45" s="44"/>
+      <c r="AG45" s="44"/>
       <c r="AH45" s="4"/>
       <c r="AI45" s="4"/>
       <c r="AJ45" s="4"/>
@@ -10770,90 +8306,34 @@
       <c r="E46" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF46" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG46" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="44"/>
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44"/>
+      <c r="S46" s="44"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="44"/>
+      <c r="AC46" s="44"/>
+      <c r="AD46" s="44"/>
+      <c r="AE46" s="44"/>
+      <c r="AF46" s="44"/>
+      <c r="AG46" s="44"/>
       <c r="AH46" s="4"/>
       <c r="AI46" s="4"/>
       <c r="AJ46" s="4"/>
@@ -10896,90 +8376,34 @@
       <c r="E47" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF47" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG47" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="44"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="44"/>
+      <c r="X47" s="44"/>
+      <c r="Y47" s="44"/>
+      <c r="Z47" s="44"/>
+      <c r="AA47" s="44"/>
+      <c r="AB47" s="44"/>
+      <c r="AC47" s="44"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="44"/>
+      <c r="AF47" s="44"/>
+      <c r="AG47" s="44"/>
       <c r="AH47" s="4"/>
       <c r="AI47" s="4"/>
       <c r="AJ47" s="4"/>
@@ -11022,90 +8446,34 @@
       <c r="E48" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF48" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG48" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="44"/>
+      <c r="S48" s="44"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="44"/>
+      <c r="V48" s="44"/>
+      <c r="W48" s="44"/>
+      <c r="X48" s="44"/>
+      <c r="Y48" s="44"/>
+      <c r="Z48" s="44"/>
+      <c r="AA48" s="44"/>
+      <c r="AB48" s="44"/>
+      <c r="AC48" s="44"/>
+      <c r="AD48" s="44"/>
+      <c r="AE48" s="44"/>
+      <c r="AF48" s="44"/>
+      <c r="AG48" s="44"/>
       <c r="AH48" s="4"/>
       <c r="AI48" s="4"/>
       <c r="AJ48" s="4"/>
@@ -11148,90 +8516,34 @@
       <c r="E49" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF49" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG49" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="44"/>
+      <c r="P49" s="44"/>
+      <c r="Q49" s="44"/>
+      <c r="R49" s="44"/>
+      <c r="S49" s="44"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="44"/>
+      <c r="V49" s="44"/>
+      <c r="W49" s="44"/>
+      <c r="X49" s="44"/>
+      <c r="Y49" s="44"/>
+      <c r="Z49" s="44"/>
+      <c r="AA49" s="44"/>
+      <c r="AB49" s="44"/>
+      <c r="AC49" s="44"/>
+      <c r="AD49" s="44"/>
+      <c r="AE49" s="44"/>
+      <c r="AF49" s="44"/>
+      <c r="AG49" s="44"/>
       <c r="AH49" s="4"/>
       <c r="AI49" s="4"/>
       <c r="AJ49" s="4"/>
@@ -11274,90 +8586,34 @@
       <c r="E50" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF50" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG50" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44"/>
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="44"/>
+      <c r="AA50" s="44"/>
+      <c r="AB50" s="44"/>
+      <c r="AC50" s="44"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
       <c r="AH50" s="4"/>
       <c r="AI50" s="4"/>
       <c r="AJ50" s="4"/>
@@ -11402,90 +8658,34 @@
       <c r="E51" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF51" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG51" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="44"/>
+      <c r="P51" s="44"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="44"/>
+      <c r="S51" s="44"/>
+      <c r="T51" s="44"/>
+      <c r="U51" s="44"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="44"/>
+      <c r="X51" s="44"/>
+      <c r="Y51" s="44"/>
+      <c r="Z51" s="44"/>
+      <c r="AA51" s="44"/>
+      <c r="AB51" s="44"/>
+      <c r="AC51" s="44"/>
+      <c r="AD51" s="44"/>
+      <c r="AE51" s="44"/>
+      <c r="AF51" s="44"/>
+      <c r="AG51" s="44"/>
       <c r="AH51" s="4"/>
       <c r="AI51" s="4"/>
       <c r="AJ51" s="4"/>
@@ -11530,90 +8730,34 @@
       <c r="E52" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="H52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="K52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="M52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="O52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="P52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="R52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="T52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="U52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="V52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="W52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="X52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF52" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG52" s="44" t="s">
-        <v>104</v>
-      </c>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="44"/>
+      <c r="P52" s="44"/>
+      <c r="Q52" s="44"/>
+      <c r="R52" s="44"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="44"/>
+      <c r="V52" s="44"/>
+      <c r="W52" s="44"/>
+      <c r="X52" s="44"/>
+      <c r="Y52" s="44"/>
+      <c r="Z52" s="44"/>
+      <c r="AA52" s="44"/>
+      <c r="AB52" s="44"/>
+      <c r="AC52" s="44"/>
+      <c r="AD52" s="44"/>
+      <c r="AE52" s="44"/>
+      <c r="AF52" s="44"/>
+      <c r="AG52" s="44"/>
       <c r="AH52" s="42"/>
       <c r="AI52" s="42"/>
       <c r="AJ52" s="42"/>
@@ -11648,7 +8792,7 @@
   </sheetData>
   <autoFilter ref="BI1:BJ44" xr:uid="{760E9C2D-868A-418F-9F2D-C2B8E259D30D}"/>
   <conditionalFormatting sqref="BE2:BG52">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11926,11 +9070,11 @@
       </c>
       <c r="K2" s="8">
         <f>SUM(M7:AC7)</f>
-        <v>867</v>
+        <v>51</v>
       </c>
       <c r="L2" s="8">
         <f>AVERAGE(M2:AJ2)</f>
-        <v>1.7586206896551724</v>
+        <v>7.3275862068965511E-2</v>
       </c>
       <c r="M2" s="8">
         <f t="shared" ref="M2:AR2" si="0">M7/$F$2</f>
@@ -11938,115 +9082,115 @@
       </c>
       <c r="N2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="O2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="P2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="R2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="S2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="T2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="U2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="V2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="W2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="X2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="8">
         <f t="shared" si="0"/>
-        <v>1.7586206896551724</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="8">
         <f t="shared" si="0"/>
@@ -12424,115 +9568,115 @@
       </c>
       <c r="N7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!F2:F67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!G2:G67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="P7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!H2:H67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!I2:I67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!J2:J67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!K2:K67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="T7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!L2:L67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="U7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!M2:M67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="V7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!N2:N67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="W7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!O2:O67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="X7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!P2:P67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Q2:Q67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!R2:R67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!S2:S67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!T2:T67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!U2:U67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!V2:V67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!W2:W67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!X2:X67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Y2:Y67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Z2:Z67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AA2:AA67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AB2:AB67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AC2:AC67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AD2:AD67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AE2:AE67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AF2:AF67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AG2:AG67)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AH2:AH67)</f>
@@ -16692,12 +13836,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C20">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE2:BG43">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16714,6 +13858,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9e324e9-4967-437b-a497-16f662c21391">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="dcbe9599-1178-413b-9602-83ebc6e8bce4" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DocumentCategory xmlns="e7640078-2807-4792-8712-763d4cb58983" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D45F55DA03AD8849999218AD871CBDF0" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3a836707be849dfa7ce4683be2486502">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="e7640078-2807-4792-8712-763d4cb58983" xmlns:ns3="dcbe9599-1178-413b-9602-83ebc6e8bce4" xmlns:ns4="e9e324e9-4967-437b-a497-16f662c21391" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f940417f33b8f1f2ce4246c9e35d0ae" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -16986,34 +14153,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9e324e9-4967-437b-a497-16f662c21391">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="dcbe9599-1178-413b-9602-83ebc6e8bce4" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DocumentCategory xmlns="e7640078-2807-4792-8712-763d4cb58983" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A07560-16E1-4559-8CE1-6DDA79DFE9DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="e9e324e9-4967-437b-a497-16f662c21391"/>
+    <ds:schemaRef ds:uri="dcbe9599-1178-413b-9602-83ebc6e8bce4"/>
+    <ds:schemaRef ds:uri="e7640078-2807-4792-8712-763d4cb58983"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BA007C-FCAF-45A2-BE18-B36EE22CEF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65533DC7-38B6-47C2-9AFD-406A18AF675D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17034,27 +14199,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BA007C-FCAF-45A2-BE18-B36EE22CEF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A07560-16E1-4559-8CE1-6DDA79DFE9DD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="e9e324e9-4967-437b-a497-16f662c21391"/>
-    <ds:schemaRef ds:uri="dcbe9599-1178-413b-9602-83ebc6e8bce4"/>
-    <ds:schemaRef ds:uri="e7640078-2807-4792-8712-763d4cb58983"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D875DB42-104D-4A36-925C-E0DD5B997017}">
   <ds:schemaRefs>

--- a/docs/specs/StatusReportBI_2026.xlsx
+++ b/docs/specs/StatusReportBI_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diogofaria/Documents/Azure-NHB/nhb-project-delivery/docs/specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D29C40-7F16-754F-A646-C650B136F5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A36016-01EB-C847-97F2-1EFC37886F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" tabRatio="338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StatusReport_2026_NovaFormula" sheetId="12" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="246">
   <si>
     <t>Project ID</t>
   </si>
@@ -983,6 +983,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1719,7 +1722,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1787,6 +1790,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="14" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1834,6 +1838,540 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="121">
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3414,540 +3952,6 @@
       <font>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -4105,128 +4109,128 @@
     <tableColumn id="3" xr3:uid="{63642D60-CB02-45D4-BF90-C551A73005E7}" name="Status Projeto" dataDxfId="116"/>
     <tableColumn id="4" xr3:uid="{E95A609A-A81B-45BC-B3B9-07FFCB208FAF}" name="Responsável pelo Envio" dataDxfId="115" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{95099C14-44CF-4DF9-B110-9C242326F4CA}" name="Semana 1" dataDxfId="114" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{73414AEB-ABC1-4A6A-9CFA-6ED9C059DCAF}" name="Semana 2" dataDxfId="113" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{122FFB43-8DB4-4E9E-B22F-D7ADC7687ECE}" name="Semana 3" dataDxfId="112" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{1E7C0653-A3EF-4816-957A-20E6F2B21AF2}" name="Semana 4" dataDxfId="111" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{1154A540-4FCB-4780-8A79-F70769F72D06}" name="Semana 5" dataDxfId="110" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{95D5B214-2B54-4364-8368-63D22D61234F}" name="Semana 6" dataDxfId="109" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{65D198C8-B714-4D67-8CD9-20B9A69B14A8}" name="Semana 7" dataDxfId="108" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{9F8773A6-C0B8-46FB-A9A5-F8C7663AAB72}" name="Semana 8" dataDxfId="107" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{DB086BC0-A2E6-4B72-9E18-0A2773B3BDEC}" name="Semana 9" dataDxfId="106" dataCellStyle="Normal"/>
-    <tableColumn id="14" xr3:uid="{03482946-921A-489E-9B6E-13A09D34521F}" name="Semana 10" dataDxfId="105" dataCellStyle="Normal"/>
-    <tableColumn id="15" xr3:uid="{36E37EF5-1859-4D70-A226-00032CDBE725}" name="Semana 11" dataDxfId="104" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{EA28C418-2D0C-4407-8DEA-6BED9D1F13CD}" name="Semana 12" dataDxfId="103" dataCellStyle="Normal"/>
-    <tableColumn id="17" xr3:uid="{03E48B39-D02B-4107-AC9B-850BF98D70F1}" name="Semana 13" dataDxfId="102" dataCellStyle="Normal"/>
-    <tableColumn id="18" xr3:uid="{3016A65B-31F8-4B15-AEEF-74725A05E045}" name="Semana 14" dataDxfId="101" dataCellStyle="Normal"/>
-    <tableColumn id="19" xr3:uid="{0148934D-5053-41B7-A64C-6ECEE770522E}" name="Semana 15" dataDxfId="100" dataCellStyle="Normal"/>
-    <tableColumn id="20" xr3:uid="{9DE17A1F-203B-4603-B5B8-0F73840A571D}" name="Semana 16" dataDxfId="99" dataCellStyle="Normal"/>
-    <tableColumn id="21" xr3:uid="{4967A8CE-8AFC-4D25-82EB-3306AF40FA4D}" name="Semana 17" dataDxfId="98" dataCellStyle="Normal"/>
-    <tableColumn id="22" xr3:uid="{F5338EA1-8715-4EB8-8099-1305BB6C982A}" name="Semana 18" dataDxfId="97" dataCellStyle="Normal"/>
-    <tableColumn id="23" xr3:uid="{495CA1A8-9DB6-4D29-BBED-C2E6348B3CE4}" name="Semana 19" dataDxfId="96" dataCellStyle="Normal"/>
-    <tableColumn id="24" xr3:uid="{E7125378-96DB-4D78-85E8-5C7C30485827}" name="Semana 20" dataDxfId="95" dataCellStyle="Normal"/>
-    <tableColumn id="25" xr3:uid="{3A40A1FA-9A58-48F2-9956-BD8778E33B35}" name="Semana 21" dataDxfId="94" dataCellStyle="Normal"/>
-    <tableColumn id="26" xr3:uid="{CC488376-5634-40F7-A570-73F74BCC52C9}" name="Semana 22" dataDxfId="93" dataCellStyle="Normal"/>
-    <tableColumn id="27" xr3:uid="{3C318C5C-FEDD-45B7-AB98-52F9865ED23F}" name="Semana 23" dataDxfId="92" dataCellStyle="Normal"/>
-    <tableColumn id="28" xr3:uid="{0AAEB85E-2EBA-4F3D-9DA5-F641D0795AD5}" name="Semana 24" dataDxfId="91" dataCellStyle="Normal"/>
-    <tableColumn id="29" xr3:uid="{15A3A05F-39E6-4114-8E21-8948D6D215B6}" name="Semana 25" dataDxfId="90" dataCellStyle="Normal"/>
-    <tableColumn id="30" xr3:uid="{82ED50ED-A64E-4DE7-8234-E87F8E1EF798}" name="Semana 26" dataDxfId="89" dataCellStyle="Normal"/>
-    <tableColumn id="31" xr3:uid="{BAF65312-CFFF-44AE-9138-5D3A6D27E7C7}" name="Semana 27" dataDxfId="88" dataCellStyle="Normal"/>
-    <tableColumn id="32" xr3:uid="{A740F5FB-84C5-4A56-9A8D-D7992F2DF04D}" name="Semana 28" dataDxfId="87" dataCellStyle="Normal"/>
-    <tableColumn id="33" xr3:uid="{B574E1B2-4909-4AD3-9F06-4B1258242DB3}" name="Semana 29" dataDxfId="86" dataCellStyle="Normal"/>
-    <tableColumn id="34" xr3:uid="{6B841F49-49FD-4D60-B298-ACACAFE16783}" name="Semana 30" dataDxfId="85" dataCellStyle="Normal"/>
-    <tableColumn id="35" xr3:uid="{7775AB51-894F-451C-8868-0EA34C0DEF51}" name="Semana 31" dataDxfId="84" dataCellStyle="Normal"/>
-    <tableColumn id="36" xr3:uid="{D7E75888-0F8F-4BF3-AADA-273C4A0C85F4}" name="Semana 32" dataDxfId="83" dataCellStyle="Normal"/>
-    <tableColumn id="37" xr3:uid="{45AD0369-8FF4-45E2-9A72-A52C5CA873E3}" name="Semana 33" dataDxfId="82" dataCellStyle="Normal"/>
-    <tableColumn id="38" xr3:uid="{C5F33218-0780-4982-B1BD-C98114844466}" name="Semana 34" dataDxfId="81" dataCellStyle="Normal"/>
-    <tableColumn id="39" xr3:uid="{9A87502B-AB25-4DEE-A852-2EB6CB627ED5}" name="Semana 35" dataDxfId="80" dataCellStyle="Normal"/>
-    <tableColumn id="40" xr3:uid="{43993064-1F0B-42B0-8910-20411F7D5206}" name="Semana 36" dataDxfId="79" dataCellStyle="Normal"/>
-    <tableColumn id="41" xr3:uid="{8FA42040-EE3D-4B55-9FCF-94904F31B067}" name="Semana 37" dataDxfId="78" dataCellStyle="Normal"/>
-    <tableColumn id="42" xr3:uid="{BF992F4E-A115-475B-895A-1D33CFA3B5AE}" name="Semana 38" dataDxfId="77" dataCellStyle="Normal"/>
-    <tableColumn id="43" xr3:uid="{094398BA-73C4-4D4E-B5C5-B732C46BB5AC}" name="Semana 39" dataDxfId="76" dataCellStyle="Normal"/>
-    <tableColumn id="44" xr3:uid="{093D68FD-B45A-4175-A81E-1802F10A5F2B}" name="Semana 40" dataDxfId="75" dataCellStyle="Normal"/>
-    <tableColumn id="45" xr3:uid="{EF9413F4-133C-4D71-9376-15B16CF6D450}" name="Semana 41" dataDxfId="74" dataCellStyle="Normal"/>
-    <tableColumn id="46" xr3:uid="{ED936B61-8F48-49B8-B05F-D81645FCAFFA}" name="Semana 42" dataDxfId="73" dataCellStyle="Normal"/>
-    <tableColumn id="47" xr3:uid="{27CBDBAC-4916-406F-8E7E-0A96CE34203C}" name="Semana 43" dataDxfId="72" dataCellStyle="Normal"/>
-    <tableColumn id="48" xr3:uid="{BC1B5741-A3D0-4F2E-9514-221D71F4D87D}" name="Semana 44" dataDxfId="71" dataCellStyle="Normal"/>
-    <tableColumn id="49" xr3:uid="{3F463363-3716-4230-B5F9-A8425BB1BBFD}" name="Semana 45" dataDxfId="70" dataCellStyle="Normal"/>
-    <tableColumn id="50" xr3:uid="{B21BE339-C896-4291-925E-91832D88BD3B}" name="Semana 46" dataDxfId="69" dataCellStyle="Normal"/>
-    <tableColumn id="51" xr3:uid="{4978273D-36B6-40A4-9E59-57BECD4F31CC}" name="Semana 47" dataDxfId="68" dataCellStyle="Normal"/>
-    <tableColumn id="52" xr3:uid="{BE0BD3B9-6E97-48B1-8FF2-EEE0915D3137}" name="Semana 48" dataDxfId="67" dataCellStyle="Normal"/>
-    <tableColumn id="53" xr3:uid="{FED24952-113C-4790-993E-3B5172B319B2}" name="Semana 49" dataDxfId="66" dataCellStyle="Normal"/>
-    <tableColumn id="54" xr3:uid="{FF8CD072-9365-498B-9E7E-2CBDF528A19B}" name="Semana 50" dataDxfId="65" dataCellStyle="Normal"/>
-    <tableColumn id="55" xr3:uid="{A9D5CE35-E74A-4CD9-BA33-ECA5C406AB38}" name="Semana 51" dataDxfId="64" dataCellStyle="Normal"/>
-    <tableColumn id="56" xr3:uid="{C086F1D6-06DB-46AF-9DDF-4E460E8BD8E0}" name="Semana 52" dataDxfId="63" dataCellStyle="Normal"/>
-    <tableColumn id="57" xr3:uid="{C942B3B3-E3B6-4201-82B8-5641A2709F68}" name="Total de Status nas Semanas" dataDxfId="62" dataCellStyle="Normal"/>
-    <tableColumn id="58" xr3:uid="{4EEC2AEC-C5B4-460B-A06F-F44BA640360A}" name="Total de status não enviados" dataDxfId="61" dataCellStyle="Normal"/>
-    <tableColumn id="59" xr3:uid="{F27A72D0-C6D2-4CAE-8C97-0F94070EA169}" name="Total que deveria ter sido enviado" dataDxfId="60" dataCellStyle="Normal"/>
-    <tableColumn id="60" xr3:uid="{F935478D-2905-48CF-88A8-01F8D0043E04}" name="OBS" dataDxfId="59" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{73414AEB-ABC1-4A6A-9CFA-6ED9C059DCAF}" name="Semana 2" dataDxfId="23" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{122FFB43-8DB4-4E9E-B22F-D7ADC7687ECE}" name="Semana 3" dataDxfId="22" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{1E7C0653-A3EF-4816-957A-20E6F2B21AF2}" name="Semana 4" dataDxfId="21" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{1154A540-4FCB-4780-8A79-F70769F72D06}" name="Semana 5" dataDxfId="20" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{95D5B214-2B54-4364-8368-63D22D61234F}" name="Semana 6" dataDxfId="19" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{65D198C8-B714-4D67-8CD9-20B9A69B14A8}" name="Semana 7" dataDxfId="18" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{9F8773A6-C0B8-46FB-A9A5-F8C7663AAB72}" name="Semana 8" dataDxfId="17" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{DB086BC0-A2E6-4B72-9E18-0A2773B3BDEC}" name="Semana 9" dataDxfId="16" dataCellStyle="Normal"/>
+    <tableColumn id="14" xr3:uid="{03482946-921A-489E-9B6E-13A09D34521F}" name="Semana 10" dataDxfId="15" dataCellStyle="Normal"/>
+    <tableColumn id="15" xr3:uid="{36E37EF5-1859-4D70-A226-00032CDBE725}" name="Semana 11" dataDxfId="14" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{EA28C418-2D0C-4407-8DEA-6BED9D1F13CD}" name="Semana 12" dataDxfId="13" dataCellStyle="Normal"/>
+    <tableColumn id="17" xr3:uid="{03E48B39-D02B-4107-AC9B-850BF98D70F1}" name="Semana 13" dataDxfId="12" dataCellStyle="Normal"/>
+    <tableColumn id="18" xr3:uid="{3016A65B-31F8-4B15-AEEF-74725A05E045}" name="Semana 14" dataDxfId="11" dataCellStyle="Normal"/>
+    <tableColumn id="19" xr3:uid="{0148934D-5053-41B7-A64C-6ECEE770522E}" name="Semana 15" dataDxfId="10" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{9DE17A1F-203B-4603-B5B8-0F73840A571D}" name="Semana 16" dataDxfId="9" dataCellStyle="Normal"/>
+    <tableColumn id="21" xr3:uid="{4967A8CE-8AFC-4D25-82EB-3306AF40FA4D}" name="Semana 17" dataDxfId="8" dataCellStyle="Normal"/>
+    <tableColumn id="22" xr3:uid="{F5338EA1-8715-4EB8-8099-1305BB6C982A}" name="Semana 18" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="23" xr3:uid="{495CA1A8-9DB6-4D29-BBED-C2E6348B3CE4}" name="Semana 19" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="24" xr3:uid="{E7125378-96DB-4D78-85E8-5C7C30485827}" name="Semana 20" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="25" xr3:uid="{3A40A1FA-9A58-48F2-9956-BD8778E33B35}" name="Semana 21" dataDxfId="4" dataCellStyle="Normal"/>
+    <tableColumn id="26" xr3:uid="{CC488376-5634-40F7-A570-73F74BCC52C9}" name="Semana 22" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="27" xr3:uid="{3C318C5C-FEDD-45B7-AB98-52F9865ED23F}" name="Semana 23" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="28" xr3:uid="{0AAEB85E-2EBA-4F3D-9DA5-F641D0795AD5}" name="Semana 24" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="29" xr3:uid="{15A3A05F-39E6-4114-8E21-8948D6D215B6}" name="Semana 25" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="30" xr3:uid="{82ED50ED-A64E-4DE7-8234-E87F8E1EF798}" name="Semana 26" dataDxfId="113" dataCellStyle="Normal"/>
+    <tableColumn id="31" xr3:uid="{BAF65312-CFFF-44AE-9138-5D3A6D27E7C7}" name="Semana 27" dataDxfId="112" dataCellStyle="Normal"/>
+    <tableColumn id="32" xr3:uid="{A740F5FB-84C5-4A56-9A8D-D7992F2DF04D}" name="Semana 28" dataDxfId="111" dataCellStyle="Normal"/>
+    <tableColumn id="33" xr3:uid="{B574E1B2-4909-4AD3-9F06-4B1258242DB3}" name="Semana 29" dataDxfId="110" dataCellStyle="Normal"/>
+    <tableColumn id="34" xr3:uid="{6B841F49-49FD-4D60-B298-ACACAFE16783}" name="Semana 30" dataDxfId="109" dataCellStyle="Normal"/>
+    <tableColumn id="35" xr3:uid="{7775AB51-894F-451C-8868-0EA34C0DEF51}" name="Semana 31" dataDxfId="108" dataCellStyle="Normal"/>
+    <tableColumn id="36" xr3:uid="{D7E75888-0F8F-4BF3-AADA-273C4A0C85F4}" name="Semana 32" dataDxfId="107" dataCellStyle="Normal"/>
+    <tableColumn id="37" xr3:uid="{45AD0369-8FF4-45E2-9A72-A52C5CA873E3}" name="Semana 33" dataDxfId="106" dataCellStyle="Normal"/>
+    <tableColumn id="38" xr3:uid="{C5F33218-0780-4982-B1BD-C98114844466}" name="Semana 34" dataDxfId="105" dataCellStyle="Normal"/>
+    <tableColumn id="39" xr3:uid="{9A87502B-AB25-4DEE-A852-2EB6CB627ED5}" name="Semana 35" dataDxfId="104" dataCellStyle="Normal"/>
+    <tableColumn id="40" xr3:uid="{43993064-1F0B-42B0-8910-20411F7D5206}" name="Semana 36" dataDxfId="103" dataCellStyle="Normal"/>
+    <tableColumn id="41" xr3:uid="{8FA42040-EE3D-4B55-9FCF-94904F31B067}" name="Semana 37" dataDxfId="102" dataCellStyle="Normal"/>
+    <tableColumn id="42" xr3:uid="{BF992F4E-A115-475B-895A-1D33CFA3B5AE}" name="Semana 38" dataDxfId="101" dataCellStyle="Normal"/>
+    <tableColumn id="43" xr3:uid="{094398BA-73C4-4D4E-B5C5-B732C46BB5AC}" name="Semana 39" dataDxfId="100" dataCellStyle="Normal"/>
+    <tableColumn id="44" xr3:uid="{093D68FD-B45A-4175-A81E-1802F10A5F2B}" name="Semana 40" dataDxfId="99" dataCellStyle="Normal"/>
+    <tableColumn id="45" xr3:uid="{EF9413F4-133C-4D71-9376-15B16CF6D450}" name="Semana 41" dataDxfId="98" dataCellStyle="Normal"/>
+    <tableColumn id="46" xr3:uid="{ED936B61-8F48-49B8-B05F-D81645FCAFFA}" name="Semana 42" dataDxfId="97" dataCellStyle="Normal"/>
+    <tableColumn id="47" xr3:uid="{27CBDBAC-4916-406F-8E7E-0A96CE34203C}" name="Semana 43" dataDxfId="96" dataCellStyle="Normal"/>
+    <tableColumn id="48" xr3:uid="{BC1B5741-A3D0-4F2E-9514-221D71F4D87D}" name="Semana 44" dataDxfId="95" dataCellStyle="Normal"/>
+    <tableColumn id="49" xr3:uid="{3F463363-3716-4230-B5F9-A8425BB1BBFD}" name="Semana 45" dataDxfId="94" dataCellStyle="Normal"/>
+    <tableColumn id="50" xr3:uid="{B21BE339-C896-4291-925E-91832D88BD3B}" name="Semana 46" dataDxfId="93" dataCellStyle="Normal"/>
+    <tableColumn id="51" xr3:uid="{4978273D-36B6-40A4-9E59-57BECD4F31CC}" name="Semana 47" dataDxfId="92" dataCellStyle="Normal"/>
+    <tableColumn id="52" xr3:uid="{BE0BD3B9-6E97-48B1-8FF2-EEE0915D3137}" name="Semana 48" dataDxfId="91" dataCellStyle="Normal"/>
+    <tableColumn id="53" xr3:uid="{FED24952-113C-4790-993E-3B5172B319B2}" name="Semana 49" dataDxfId="90" dataCellStyle="Normal"/>
+    <tableColumn id="54" xr3:uid="{FF8CD072-9365-498B-9E7E-2CBDF528A19B}" name="Semana 50" dataDxfId="89" dataCellStyle="Normal"/>
+    <tableColumn id="55" xr3:uid="{A9D5CE35-E74A-4CD9-BA33-ECA5C406AB38}" name="Semana 51" dataDxfId="88" dataCellStyle="Normal"/>
+    <tableColumn id="56" xr3:uid="{C086F1D6-06DB-46AF-9DDF-4E460E8BD8E0}" name="Semana 52" dataDxfId="87" dataCellStyle="Normal"/>
+    <tableColumn id="57" xr3:uid="{C942B3B3-E3B6-4201-82B8-5641A2709F68}" name="Total de Status nas Semanas" dataDxfId="86" dataCellStyle="Normal"/>
+    <tableColumn id="58" xr3:uid="{4EEC2AEC-C5B4-460B-A06F-F44BA640360A}" name="Total de status não enviados" dataDxfId="85" dataCellStyle="Normal"/>
+    <tableColumn id="59" xr3:uid="{F27A72D0-C6D2-4CAE-8C97-0F94070EA169}" name="Total que deveria ter sido enviado" dataDxfId="84" dataCellStyle="Normal"/>
+    <tableColumn id="60" xr3:uid="{F935478D-2905-48CF-88A8-01F8D0043E04}" name="OBS" dataDxfId="83" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81E4E6BB-0F5E-4E4D-9851-E6D3C097EB26}" name="tbl_StatusReport2" displayName="tbl_StatusReport2" ref="A1:BH43" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{81E4E6BB-0F5E-4E4D-9851-E6D3C097EB26}" name="tbl_StatusReport2" displayName="tbl_StatusReport2" ref="A1:BH43" totalsRowShown="0" headerRowDxfId="82">
   <autoFilter ref="A1:BH43" xr:uid="{83E74578-6452-4198-8AF3-C0841F627FE0}"/>
   <tableColumns count="60">
     <tableColumn id="1" xr3:uid="{60644CF8-7FC5-47A9-8F97-C081DF7E0D50}" name="Project ID" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{C2AF5DF4-E408-4A0F-B0FF-D3F1D949D995}" name="Project Name" dataCellStyle="Normal"/>
     <tableColumn id="3" xr3:uid="{C40CFA33-177C-4A0E-B079-EFC40DAB6BC5}" name="Status Projeto" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{B067411B-105E-459A-A1F3-21C5FDF1CD52}" name="Resposnável pelo Envio" dataDxfId="57" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{B95BED59-99A7-436F-AC30-A28EBCCA6931}" name="Semana 1" dataDxfId="56" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{AA50DD29-3BD2-4412-B8CA-5D2D63F23E00}" name="Semana 2" dataDxfId="55" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{50862FA4-D291-4946-95C7-BF84D25DEDD2}" name="Semana 3" dataDxfId="54" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{7C2FAF54-DB38-4B15-875F-687B7CA3D9DB}" name="Semana 4" dataDxfId="53" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{E7FBD991-572B-437F-9490-CF7F73F2802B}" name="Semana 5" dataDxfId="52" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{ADEA988C-51D7-4E69-8A79-3B2240A433F1}" name="Semana 6" dataDxfId="51" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{77DB9460-2902-4E0A-B35B-A011DEA9E930}" name="Semana 7" dataDxfId="50" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{88504A38-4176-4622-8A62-7F35DAD02FD8}" name="Semana 8" dataDxfId="49" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{84A6395D-BC23-4C3D-B4DB-A2766FFFC887}" name="Semana 9" dataDxfId="48" dataCellStyle="Normal"/>
-    <tableColumn id="14" xr3:uid="{C615CFA6-862C-450D-8227-7B01CBA54D31}" name="Semana 10" dataDxfId="47" dataCellStyle="Normal"/>
-    <tableColumn id="15" xr3:uid="{B850C858-77F5-4FDA-B1B3-67E98753E073}" name="Semana 11" dataDxfId="46" dataCellStyle="Normal"/>
-    <tableColumn id="16" xr3:uid="{5B024900-3FE2-427A-8C1F-EDE695A2F073}" name="Semana 12" dataDxfId="45" dataCellStyle="Normal"/>
-    <tableColumn id="17" xr3:uid="{7E1C5632-B6C3-4F84-B269-653123E54573}" name="Semana 13" dataDxfId="44" dataCellStyle="Normal"/>
-    <tableColumn id="18" xr3:uid="{FDE37690-441F-40CF-871D-D8E32B78AB65}" name="Semana 14" dataDxfId="43" dataCellStyle="Normal"/>
-    <tableColumn id="19" xr3:uid="{4B879AF5-BDD8-4CCE-BC4D-EEB14F5C4FE6}" name="Semana 15" dataDxfId="42" dataCellStyle="Normal"/>
-    <tableColumn id="20" xr3:uid="{88BF33A8-3F7E-4A07-A77D-DEC63A3E1509}" name="Semana 16" dataDxfId="41" dataCellStyle="Normal"/>
-    <tableColumn id="21" xr3:uid="{1403F70F-7A64-4AC8-8535-15D6D8BDB4B9}" name="Semana 17" dataDxfId="40" dataCellStyle="Normal"/>
-    <tableColumn id="22" xr3:uid="{ECD4A88B-FE92-44FC-B7B8-3B4051F3308E}" name="Semana 18" dataDxfId="39" dataCellStyle="Normal"/>
-    <tableColumn id="23" xr3:uid="{F786310B-6FBB-4243-A793-0F09B01CA51B}" name="Semana 19" dataDxfId="38" dataCellStyle="Normal"/>
-    <tableColumn id="24" xr3:uid="{3A82CE0E-C593-45FD-87A7-A10A2204BDD7}" name="Semana 20" dataDxfId="37" dataCellStyle="Normal"/>
-    <tableColumn id="25" xr3:uid="{68BFF4E4-666B-4869-9A5B-CDA95C7FCEC7}" name="Semana 21" dataDxfId="36" dataCellStyle="Normal"/>
-    <tableColumn id="26" xr3:uid="{0EBA6F0D-9236-4C6E-A272-5F35D0EC5AB1}" name="Semana 22" dataDxfId="35" dataCellStyle="Normal"/>
-    <tableColumn id="27" xr3:uid="{EA331F7A-2713-4B9A-8BE4-4D02293B94D1}" name="Semana 23" dataDxfId="34" dataCellStyle="Normal"/>
-    <tableColumn id="28" xr3:uid="{F9E988BA-9C7F-4DA2-A9E9-29D34ADA88B8}" name="Semana 24" dataDxfId="33" dataCellStyle="Normal"/>
-    <tableColumn id="29" xr3:uid="{FCB56C4C-13F5-4BC5-86B1-03980E2095E4}" name="Semana 25" dataDxfId="32" dataCellStyle="Normal"/>
-    <tableColumn id="30" xr3:uid="{8E849DFF-59E7-434F-889D-C41E8C12990E}" name="Semana 26" dataDxfId="31" dataCellStyle="Normal"/>
-    <tableColumn id="31" xr3:uid="{3E22461B-7491-4D06-9C1D-AA584C13527A}" name="Semana 27" dataDxfId="30" dataCellStyle="Normal"/>
-    <tableColumn id="32" xr3:uid="{9E8D9E17-F503-435F-9640-A9CE2F572BDB}" name="Semana 28" dataDxfId="29" dataCellStyle="Normal"/>
-    <tableColumn id="33" xr3:uid="{73E0A55D-D20F-4CE7-AA47-08846AD9334E}" name="Semana 29" dataDxfId="28" dataCellStyle="Normal"/>
-    <tableColumn id="34" xr3:uid="{347728D7-EE6E-4DB2-820D-EDEA42978F39}" name="Semana 30" dataDxfId="27" dataCellStyle="Normal"/>
-    <tableColumn id="35" xr3:uid="{44E5172E-706C-4C6F-B8EA-B3EC54F01EB0}" name="Semana 31" dataDxfId="26" dataCellStyle="Normal"/>
-    <tableColumn id="36" xr3:uid="{C842825A-9412-4AB0-830C-41A75F2B05E9}" name="Semana 32" dataDxfId="25" dataCellStyle="Normal"/>
-    <tableColumn id="37" xr3:uid="{9BE5AE3B-2B4F-48CE-B0D8-2CA714EBA5AA}" name="Semana 33" dataDxfId="24" dataCellStyle="Normal"/>
-    <tableColumn id="38" xr3:uid="{64947CDC-1740-43D0-BBC7-5DF40FE818DB}" name="Semana 34" dataDxfId="23" dataCellStyle="Normal"/>
-    <tableColumn id="39" xr3:uid="{6E9FFA5C-C002-4015-AC26-ADE6FD7BD69F}" name="Semana 35" dataDxfId="22" dataCellStyle="Normal"/>
-    <tableColumn id="40" xr3:uid="{8C851BDB-E328-41E3-8D67-B236D267C287}" name="Semana 36" dataDxfId="21" dataCellStyle="Normal"/>
-    <tableColumn id="41" xr3:uid="{E21EA4CD-8EDF-4B55-8961-16519034BD4E}" name="Semana 37" dataDxfId="20" dataCellStyle="Normal"/>
-    <tableColumn id="42" xr3:uid="{B6573B96-9C38-4F68-B9B8-682581FADBC6}" name="Semana 38" dataDxfId="19" dataCellStyle="Normal"/>
-    <tableColumn id="43" xr3:uid="{EB8E5AAE-406E-428F-8F43-E9CCC85E95B7}" name="Semana 39" dataDxfId="18" dataCellStyle="Normal"/>
-    <tableColumn id="44" xr3:uid="{12200613-60B9-40AC-982D-CB89B99C2521}" name="Semana 40" dataDxfId="17" dataCellStyle="Normal"/>
-    <tableColumn id="45" xr3:uid="{6C5EF691-5409-400E-B3FB-D2FE35FD9F60}" name="Semana 41" dataDxfId="16" dataCellStyle="Normal"/>
-    <tableColumn id="46" xr3:uid="{0DE71B90-7FB4-4EA4-B156-9F327948F5B3}" name="Semana 42" dataDxfId="15" dataCellStyle="Normal"/>
-    <tableColumn id="47" xr3:uid="{E80A05C4-33DB-4CDA-B5AC-9475DAA59C1D}" name="Semana 43" dataDxfId="14" dataCellStyle="Normal"/>
-    <tableColumn id="48" xr3:uid="{A13DC0AC-4020-4D91-88A2-A3CF5023D71E}" name="Semana 44" dataDxfId="13" dataCellStyle="Normal"/>
-    <tableColumn id="49" xr3:uid="{A129B4C7-FEA3-4455-876A-8598B5495606}" name="Semana 45" dataDxfId="12" dataCellStyle="Normal"/>
-    <tableColumn id="50" xr3:uid="{5E4DC677-E036-42BE-A97F-5DAB924E573D}" name="Semana 46" dataDxfId="11" dataCellStyle="Normal"/>
-    <tableColumn id="51" xr3:uid="{A67EE59D-51AB-40D8-9CE3-DB8524EC975F}" name="Semana 47" dataDxfId="10" dataCellStyle="Normal"/>
-    <tableColumn id="52" xr3:uid="{3A58EC60-C207-4911-81D8-91540AD1ED46}" name="Semana 48" dataDxfId="9" dataCellStyle="Normal"/>
-    <tableColumn id="53" xr3:uid="{40541B89-AE21-4406-B4FA-25E62DC9FA1B}" name="Semana 49" dataDxfId="8" dataCellStyle="Normal"/>
-    <tableColumn id="54" xr3:uid="{30EF9924-92E3-43A3-B133-E547C044E2E3}" name="Semana 50" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="55" xr3:uid="{9B7F822E-7A2C-4EE0-8027-D60A40614815}" name="Semana 51" dataDxfId="6" dataCellStyle="Normal"/>
-    <tableColumn id="56" xr3:uid="{B949C798-3D55-4A69-AB99-63103C551AB7}" name="Semana 52" dataDxfId="5" dataCellStyle="Normal"/>
-    <tableColumn id="57" xr3:uid="{6E7C401A-C5D4-4B4D-9497-9B2289A4E425}" name="Total de Status nas Semanas" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="58" xr3:uid="{6B89C980-EBAD-4DCE-BA8F-204316393746}" name="Total de status não enviados" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{B067411B-105E-459A-A1F3-21C5FDF1CD52}" name="Resposnável pelo Envio" dataDxfId="81" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{B95BED59-99A7-436F-AC30-A28EBCCA6931}" name="Semana 1" dataDxfId="80" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{AA50DD29-3BD2-4412-B8CA-5D2D63F23E00}" name="Semana 2" dataDxfId="79" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{50862FA4-D291-4946-95C7-BF84D25DEDD2}" name="Semana 3" dataDxfId="78" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{7C2FAF54-DB38-4B15-875F-687B7CA3D9DB}" name="Semana 4" dataDxfId="77" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{E7FBD991-572B-437F-9490-CF7F73F2802B}" name="Semana 5" dataDxfId="76" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{ADEA988C-51D7-4E69-8A79-3B2240A433F1}" name="Semana 6" dataDxfId="75" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{77DB9460-2902-4E0A-B35B-A011DEA9E930}" name="Semana 7" dataDxfId="74" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{88504A38-4176-4622-8A62-7F35DAD02FD8}" name="Semana 8" dataDxfId="73" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{84A6395D-BC23-4C3D-B4DB-A2766FFFC887}" name="Semana 9" dataDxfId="72" dataCellStyle="Normal"/>
+    <tableColumn id="14" xr3:uid="{C615CFA6-862C-450D-8227-7B01CBA54D31}" name="Semana 10" dataDxfId="71" dataCellStyle="Normal"/>
+    <tableColumn id="15" xr3:uid="{B850C858-77F5-4FDA-B1B3-67E98753E073}" name="Semana 11" dataDxfId="70" dataCellStyle="Normal"/>
+    <tableColumn id="16" xr3:uid="{5B024900-3FE2-427A-8C1F-EDE695A2F073}" name="Semana 12" dataDxfId="69" dataCellStyle="Normal"/>
+    <tableColumn id="17" xr3:uid="{7E1C5632-B6C3-4F84-B269-653123E54573}" name="Semana 13" dataDxfId="68" dataCellStyle="Normal"/>
+    <tableColumn id="18" xr3:uid="{FDE37690-441F-40CF-871D-D8E32B78AB65}" name="Semana 14" dataDxfId="67" dataCellStyle="Normal"/>
+    <tableColumn id="19" xr3:uid="{4B879AF5-BDD8-4CCE-BC4D-EEB14F5C4FE6}" name="Semana 15" dataDxfId="66" dataCellStyle="Normal"/>
+    <tableColumn id="20" xr3:uid="{88BF33A8-3F7E-4A07-A77D-DEC63A3E1509}" name="Semana 16" dataDxfId="65" dataCellStyle="Normal"/>
+    <tableColumn id="21" xr3:uid="{1403F70F-7A64-4AC8-8535-15D6D8BDB4B9}" name="Semana 17" dataDxfId="64" dataCellStyle="Normal"/>
+    <tableColumn id="22" xr3:uid="{ECD4A88B-FE92-44FC-B7B8-3B4051F3308E}" name="Semana 18" dataDxfId="63" dataCellStyle="Normal"/>
+    <tableColumn id="23" xr3:uid="{F786310B-6FBB-4243-A793-0F09B01CA51B}" name="Semana 19" dataDxfId="62" dataCellStyle="Normal"/>
+    <tableColumn id="24" xr3:uid="{3A82CE0E-C593-45FD-87A7-A10A2204BDD7}" name="Semana 20" dataDxfId="61" dataCellStyle="Normal"/>
+    <tableColumn id="25" xr3:uid="{68BFF4E4-666B-4869-9A5B-CDA95C7FCEC7}" name="Semana 21" dataDxfId="60" dataCellStyle="Normal"/>
+    <tableColumn id="26" xr3:uid="{0EBA6F0D-9236-4C6E-A272-5F35D0EC5AB1}" name="Semana 22" dataDxfId="59" dataCellStyle="Normal"/>
+    <tableColumn id="27" xr3:uid="{EA331F7A-2713-4B9A-8BE4-4D02293B94D1}" name="Semana 23" dataDxfId="58" dataCellStyle="Normal"/>
+    <tableColumn id="28" xr3:uid="{F9E988BA-9C7F-4DA2-A9E9-29D34ADA88B8}" name="Semana 24" dataDxfId="57" dataCellStyle="Normal"/>
+    <tableColumn id="29" xr3:uid="{FCB56C4C-13F5-4BC5-86B1-03980E2095E4}" name="Semana 25" dataDxfId="56" dataCellStyle="Normal"/>
+    <tableColumn id="30" xr3:uid="{8E849DFF-59E7-434F-889D-C41E8C12990E}" name="Semana 26" dataDxfId="55" dataCellStyle="Normal"/>
+    <tableColumn id="31" xr3:uid="{3E22461B-7491-4D06-9C1D-AA584C13527A}" name="Semana 27" dataDxfId="54" dataCellStyle="Normal"/>
+    <tableColumn id="32" xr3:uid="{9E8D9E17-F503-435F-9640-A9CE2F572BDB}" name="Semana 28" dataDxfId="53" dataCellStyle="Normal"/>
+    <tableColumn id="33" xr3:uid="{73E0A55D-D20F-4CE7-AA47-08846AD9334E}" name="Semana 29" dataDxfId="52" dataCellStyle="Normal"/>
+    <tableColumn id="34" xr3:uid="{347728D7-EE6E-4DB2-820D-EDEA42978F39}" name="Semana 30" dataDxfId="51" dataCellStyle="Normal"/>
+    <tableColumn id="35" xr3:uid="{44E5172E-706C-4C6F-B8EA-B3EC54F01EB0}" name="Semana 31" dataDxfId="50" dataCellStyle="Normal"/>
+    <tableColumn id="36" xr3:uid="{C842825A-9412-4AB0-830C-41A75F2B05E9}" name="Semana 32" dataDxfId="49" dataCellStyle="Normal"/>
+    <tableColumn id="37" xr3:uid="{9BE5AE3B-2B4F-48CE-B0D8-2CA714EBA5AA}" name="Semana 33" dataDxfId="48" dataCellStyle="Normal"/>
+    <tableColumn id="38" xr3:uid="{64947CDC-1740-43D0-BBC7-5DF40FE818DB}" name="Semana 34" dataDxfId="47" dataCellStyle="Normal"/>
+    <tableColumn id="39" xr3:uid="{6E9FFA5C-C002-4015-AC26-ADE6FD7BD69F}" name="Semana 35" dataDxfId="46" dataCellStyle="Normal"/>
+    <tableColumn id="40" xr3:uid="{8C851BDB-E328-41E3-8D67-B236D267C287}" name="Semana 36" dataDxfId="45" dataCellStyle="Normal"/>
+    <tableColumn id="41" xr3:uid="{E21EA4CD-8EDF-4B55-8961-16519034BD4E}" name="Semana 37" dataDxfId="44" dataCellStyle="Normal"/>
+    <tableColumn id="42" xr3:uid="{B6573B96-9C38-4F68-B9B8-682581FADBC6}" name="Semana 38" dataDxfId="43" dataCellStyle="Normal"/>
+    <tableColumn id="43" xr3:uid="{EB8E5AAE-406E-428F-8F43-E9CCC85E95B7}" name="Semana 39" dataDxfId="42" dataCellStyle="Normal"/>
+    <tableColumn id="44" xr3:uid="{12200613-60B9-40AC-982D-CB89B99C2521}" name="Semana 40" dataDxfId="41" dataCellStyle="Normal"/>
+    <tableColumn id="45" xr3:uid="{6C5EF691-5409-400E-B3FB-D2FE35FD9F60}" name="Semana 41" dataDxfId="40" dataCellStyle="Normal"/>
+    <tableColumn id="46" xr3:uid="{0DE71B90-7FB4-4EA4-B156-9F327948F5B3}" name="Semana 42" dataDxfId="39" dataCellStyle="Normal"/>
+    <tableColumn id="47" xr3:uid="{E80A05C4-33DB-4CDA-B5AC-9475DAA59C1D}" name="Semana 43" dataDxfId="38" dataCellStyle="Normal"/>
+    <tableColumn id="48" xr3:uid="{A13DC0AC-4020-4D91-88A2-A3CF5023D71E}" name="Semana 44" dataDxfId="37" dataCellStyle="Normal"/>
+    <tableColumn id="49" xr3:uid="{A129B4C7-FEA3-4455-876A-8598B5495606}" name="Semana 45" dataDxfId="36" dataCellStyle="Normal"/>
+    <tableColumn id="50" xr3:uid="{5E4DC677-E036-42BE-A97F-5DAB924E573D}" name="Semana 46" dataDxfId="35" dataCellStyle="Normal"/>
+    <tableColumn id="51" xr3:uid="{A67EE59D-51AB-40D8-9CE3-DB8524EC975F}" name="Semana 47" dataDxfId="34" dataCellStyle="Normal"/>
+    <tableColumn id="52" xr3:uid="{3A58EC60-C207-4911-81D8-91540AD1ED46}" name="Semana 48" dataDxfId="33" dataCellStyle="Normal"/>
+    <tableColumn id="53" xr3:uid="{40541B89-AE21-4406-B4FA-25E62DC9FA1B}" name="Semana 49" dataDxfId="32" dataCellStyle="Normal"/>
+    <tableColumn id="54" xr3:uid="{30EF9924-92E3-43A3-B133-E547C044E2E3}" name="Semana 50" dataDxfId="31" dataCellStyle="Normal"/>
+    <tableColumn id="55" xr3:uid="{9B7F822E-7A2C-4EE0-8027-D60A40614815}" name="Semana 51" dataDxfId="30" dataCellStyle="Normal"/>
+    <tableColumn id="56" xr3:uid="{B949C798-3D55-4A69-AB99-63103C551AB7}" name="Semana 52" dataDxfId="29" dataCellStyle="Normal"/>
+    <tableColumn id="57" xr3:uid="{6E7C401A-C5D4-4B4D-9497-9B2289A4E425}" name="Total de Status nas Semanas" dataDxfId="28" dataCellStyle="Normal"/>
+    <tableColumn id="58" xr3:uid="{6B89C980-EBAD-4DCE-BA8F-204316393746}" name="Total de status não enviados" dataDxfId="27" dataCellStyle="Normal"/>
     <tableColumn id="59" xr3:uid="{97155E31-5C8F-48CC-A34F-9194D502D533}" name="Total que deveria ter sido enviado" dataCellStyle="Normal"/>
     <tableColumn id="60" xr3:uid="{63CBFB0A-8CCB-4273-AB4B-7AF1EABCA026}" name="OBS" dataCellStyle="Normal"/>
   </tableColumns>
@@ -4843,29 +4847,75 @@
       <c r="E2" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
+      <c r="F2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB2" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AC2" s="44"/>
       <c r="AD2" s="44"/>
       <c r="AE2" s="44"/>
@@ -4922,29 +4972,75 @@
       <c r="E3" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
+      <c r="F3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA3" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB3" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AC3" s="44"/>
       <c r="AD3" s="44"/>
       <c r="AE3" s="44"/>
@@ -4996,30 +5092,78 @@
       <c r="E4" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
+      <c r="F4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC4" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD4" s="44"/>
       <c r="AE4" s="44"/>
       <c r="AF4" s="44"/>
@@ -5075,30 +5219,78 @@
       <c r="E5" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
+      <c r="F5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC5" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD5" s="44"/>
       <c r="AE5" s="44"/>
       <c r="AF5" s="44"/>
@@ -5154,30 +5346,78 @@
       <c r="E6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="44"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="44"/>
-      <c r="AC6" s="44"/>
+      <c r="F6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC6" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD6" s="44"/>
       <c r="AE6" s="44"/>
       <c r="AF6" s="44"/>
@@ -5234,30 +5474,78 @@
       <c r="E7" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="44"/>
+      <c r="F7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB7" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC7" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD7" s="44"/>
       <c r="AE7" s="44"/>
       <c r="AF7" s="44"/>
@@ -5313,30 +5601,78 @@
       <c r="E8" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="44"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="44"/>
-      <c r="AC8" s="44"/>
+      <c r="F8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC8" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD8" s="44"/>
       <c r="AE8" s="44"/>
       <c r="AF8" s="44"/>
@@ -5392,30 +5728,78 @@
       <c r="E9" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
+      <c r="F9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB9" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC9" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD9" s="44"/>
       <c r="AE9" s="44"/>
       <c r="AF9" s="44"/>
@@ -5471,30 +5855,78 @@
       <c r="E10" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
+      <c r="F10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC10" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD10" s="44"/>
       <c r="AE10" s="44"/>
       <c r="AF10" s="44"/>
@@ -5550,30 +5982,78 @@
       <c r="E11" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
+      <c r="F11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC11" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD11" s="44"/>
       <c r="AE11" s="44"/>
       <c r="AF11" s="44"/>
@@ -5629,30 +6109,78 @@
       <c r="E12" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
+      <c r="F12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB12" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC12" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD12" s="44"/>
       <c r="AE12" s="44"/>
       <c r="AF12" s="44"/>
@@ -5708,30 +6236,78 @@
       <c r="E13" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44"/>
-      <c r="X13" s="44"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="44"/>
+      <c r="F13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB13" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC13" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD13" s="44"/>
       <c r="AE13" s="44"/>
       <c r="AF13" s="44"/>
@@ -5787,30 +6363,78 @@
       <c r="E14" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="44"/>
-      <c r="S14" s="44"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="44"/>
-      <c r="V14" s="44"/>
-      <c r="W14" s="44"/>
-      <c r="X14" s="44"/>
-      <c r="Y14" s="44"/>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="44"/>
-      <c r="AC14" s="44"/>
+      <c r="F14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB14" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC14" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD14" s="44"/>
       <c r="AE14" s="44"/>
       <c r="AF14" s="44"/>
@@ -5866,30 +6490,78 @@
       <c r="E15" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="44"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-      <c r="AA15" s="44"/>
-      <c r="AB15" s="44"/>
-      <c r="AC15" s="44"/>
+      <c r="F15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB15" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC15" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD15" s="44"/>
       <c r="AE15" s="44"/>
       <c r="AF15" s="44"/>
@@ -5945,30 +6617,78 @@
       <c r="E16" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="44"/>
-      <c r="U16" s="44"/>
-      <c r="V16" s="44"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="44"/>
-      <c r="Y16" s="44"/>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="44"/>
-      <c r="AC16" s="44"/>
+      <c r="F16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB16" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC16" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD16" s="44"/>
       <c r="AE16" s="44"/>
       <c r="AF16" s="44"/>
@@ -6024,30 +6744,78 @@
       <c r="E17" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44"/>
-      <c r="T17" s="44"/>
-      <c r="U17" s="44"/>
-      <c r="V17" s="44"/>
-      <c r="W17" s="44"/>
-      <c r="X17" s="44"/>
-      <c r="Y17" s="44"/>
-      <c r="Z17" s="44"/>
-      <c r="AA17" s="44"/>
-      <c r="AB17" s="44"/>
-      <c r="AC17" s="44"/>
+      <c r="F17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB17" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC17" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD17" s="44"/>
       <c r="AE17" s="44"/>
       <c r="AF17" s="44"/>
@@ -6105,30 +6873,78 @@
       <c r="E18" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="44"/>
-      <c r="W18" s="44"/>
-      <c r="X18" s="44"/>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="44"/>
-      <c r="AB18" s="44"/>
-      <c r="AC18" s="44"/>
+      <c r="F18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB18" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC18" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD18" s="44"/>
       <c r="AE18" s="44"/>
       <c r="AF18" s="44"/>
@@ -6184,30 +7000,78 @@
       <c r="E19" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
+      <c r="F19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB19" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC19" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD19" s="44"/>
       <c r="AE19" s="44"/>
       <c r="AF19" s="44"/>
@@ -6263,30 +7127,78 @@
       <c r="E20" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="44"/>
-      <c r="U20" s="44"/>
-      <c r="V20" s="44"/>
-      <c r="W20" s="44"/>
-      <c r="X20" s="44"/>
-      <c r="Y20" s="44"/>
-      <c r="Z20" s="44"/>
-      <c r="AA20" s="44"/>
-      <c r="AB20" s="44"/>
-      <c r="AC20" s="44"/>
+      <c r="F20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB20" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC20" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD20" s="44"/>
       <c r="AE20" s="44"/>
       <c r="AF20" s="44"/>
@@ -6342,30 +7254,78 @@
       <c r="E21" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
-      <c r="V21" s="44"/>
-      <c r="W21" s="44"/>
-      <c r="X21" s="44"/>
-      <c r="Y21" s="44"/>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="44"/>
-      <c r="AC21" s="44"/>
+      <c r="F21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB21" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC21" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD21" s="44"/>
       <c r="AE21" s="44"/>
       <c r="AF21" s="44"/>
@@ -6422,30 +7382,78 @@
       <c r="E22" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="44"/>
-      <c r="T22" s="44"/>
-      <c r="U22" s="44"/>
-      <c r="V22" s="44"/>
-      <c r="W22" s="44"/>
-      <c r="X22" s="44"/>
-      <c r="Y22" s="44"/>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
-      <c r="AC22" s="44"/>
+      <c r="F22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB22" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC22" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD22" s="44"/>
       <c r="AE22" s="44"/>
       <c r="AF22" s="44"/>
@@ -6503,30 +7511,78 @@
       <c r="E23" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44"/>
-      <c r="U23" s="44"/>
-      <c r="V23" s="44"/>
-      <c r="W23" s="44"/>
-      <c r="X23" s="44"/>
-      <c r="Y23" s="44"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
-      <c r="AC23" s="44"/>
+      <c r="F23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC23" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD23" s="44"/>
       <c r="AE23" s="44"/>
       <c r="AF23" s="44"/>
@@ -6582,30 +7638,78 @@
       <c r="E24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="44"/>
-      <c r="S24" s="44"/>
-      <c r="T24" s="44"/>
-      <c r="U24" s="44"/>
-      <c r="V24" s="44"/>
-      <c r="W24" s="44"/>
-      <c r="X24" s="44"/>
-      <c r="Y24" s="44"/>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="44"/>
-      <c r="AC24" s="44"/>
+      <c r="F24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB24" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC24" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD24" s="44"/>
       <c r="AE24" s="44"/>
       <c r="AF24" s="44"/>
@@ -6661,30 +7765,78 @@
       <c r="E25" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44"/>
-      <c r="V25" s="44"/>
-      <c r="W25" s="44"/>
-      <c r="X25" s="44"/>
-      <c r="Y25" s="44"/>
-      <c r="Z25" s="44"/>
-      <c r="AA25" s="44"/>
-      <c r="AB25" s="44"/>
-      <c r="AC25" s="44"/>
+      <c r="F25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC25" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD25" s="44"/>
       <c r="AE25" s="44"/>
       <c r="AF25" s="44"/>
@@ -6740,30 +7892,78 @@
       <c r="E26" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="44"/>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
-      <c r="Z26" s="44"/>
-      <c r="AA26" s="44"/>
-      <c r="AB26" s="44"/>
-      <c r="AC26" s="44"/>
+      <c r="F26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB26" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC26" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD26" s="44"/>
       <c r="AE26" s="44"/>
       <c r="AF26" s="44"/>
@@ -6819,30 +8019,78 @@
       <c r="E27" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="44"/>
-      <c r="V27" s="44"/>
-      <c r="W27" s="44"/>
-      <c r="X27" s="44"/>
-      <c r="Y27" s="44"/>
-      <c r="Z27" s="44"/>
-      <c r="AA27" s="44"/>
-      <c r="AB27" s="44"/>
-      <c r="AC27" s="44"/>
+      <c r="F27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB27" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC27" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD27" s="44"/>
       <c r="AE27" s="44"/>
       <c r="AF27" s="44"/>
@@ -6898,30 +8146,78 @@
       <c r="E28" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
+      <c r="F28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB28" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC28" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD28" s="44"/>
       <c r="AE28" s="44"/>
       <c r="AF28" s="44"/>
@@ -6977,30 +8273,78 @@
       <c r="E29" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="44"/>
-      <c r="W29" s="44"/>
-      <c r="X29" s="44"/>
-      <c r="Y29" s="44"/>
-      <c r="Z29" s="44"/>
-      <c r="AA29" s="44"/>
-      <c r="AB29" s="44"/>
-      <c r="AC29" s="44"/>
+      <c r="F29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB29" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC29" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD29" s="44"/>
       <c r="AE29" s="44"/>
       <c r="AF29" s="44"/>
@@ -7056,30 +8400,78 @@
       <c r="E30" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-      <c r="V30" s="44"/>
-      <c r="W30" s="44"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
-      <c r="Z30" s="44"/>
-      <c r="AA30" s="44"/>
-      <c r="AB30" s="44"/>
-      <c r="AC30" s="44"/>
+      <c r="F30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB30" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC30" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD30" s="44"/>
       <c r="AE30" s="44"/>
       <c r="AF30" s="44"/>
@@ -7133,30 +8525,78 @@
       <c r="E31" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-      <c r="V31" s="44"/>
-      <c r="W31" s="44"/>
-      <c r="X31" s="44"/>
-      <c r="Y31" s="44"/>
-      <c r="Z31" s="44"/>
-      <c r="AA31" s="44"/>
-      <c r="AB31" s="44"/>
-      <c r="AC31" s="44"/>
+      <c r="F31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB31" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC31" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD31" s="44"/>
       <c r="AE31" s="44"/>
       <c r="AF31" s="44"/>
@@ -7212,30 +8652,78 @@
       <c r="E32" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-      <c r="V32" s="44"/>
-      <c r="W32" s="44"/>
-      <c r="X32" s="44"/>
-      <c r="Y32" s="44"/>
-      <c r="Z32" s="44"/>
-      <c r="AA32" s="44"/>
-      <c r="AB32" s="44"/>
-      <c r="AC32" s="44"/>
+      <c r="F32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB32" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC32" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD32" s="44"/>
       <c r="AE32" s="44"/>
       <c r="AF32" s="44"/>
@@ -7291,30 +8779,78 @@
       <c r="E33" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="44"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="44"/>
-      <c r="S33" s="44"/>
-      <c r="T33" s="44"/>
-      <c r="U33" s="44"/>
-      <c r="V33" s="44"/>
-      <c r="W33" s="44"/>
-      <c r="X33" s="44"/>
-      <c r="Y33" s="44"/>
-      <c r="Z33" s="44"/>
-      <c r="AA33" s="44"/>
-      <c r="AB33" s="44"/>
-      <c r="AC33" s="44"/>
+      <c r="F33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB33" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC33" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD33" s="44"/>
       <c r="AE33" s="44"/>
       <c r="AF33" s="44"/>
@@ -7371,30 +8907,78 @@
       <c r="E34" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="44"/>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44"/>
-      <c r="V34" s="44"/>
-      <c r="W34" s="44"/>
-      <c r="X34" s="44"/>
-      <c r="Y34" s="44"/>
-      <c r="Z34" s="44"/>
-      <c r="AA34" s="44"/>
-      <c r="AB34" s="44"/>
-      <c r="AC34" s="44"/>
+      <c r="F34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB34" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC34" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD34" s="44"/>
       <c r="AE34" s="44"/>
       <c r="AF34" s="44"/>
@@ -7450,30 +9034,78 @@
       <c r="E35" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="44"/>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
-      <c r="N35" s="44"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="44"/>
-      <c r="R35" s="44"/>
-      <c r="S35" s="44"/>
-      <c r="T35" s="44"/>
-      <c r="U35" s="44"/>
-      <c r="V35" s="44"/>
-      <c r="W35" s="44"/>
-      <c r="X35" s="44"/>
-      <c r="Y35" s="44"/>
-      <c r="Z35" s="44"/>
-      <c r="AA35" s="44"/>
-      <c r="AB35" s="44"/>
-      <c r="AC35" s="44"/>
+      <c r="F35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB35" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC35" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD35" s="44"/>
       <c r="AE35" s="44"/>
       <c r="AF35" s="44"/>
@@ -7529,30 +9161,78 @@
       <c r="E36" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="44"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="44"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="44"/>
-      <c r="P36" s="44"/>
-      <c r="Q36" s="44"/>
-      <c r="R36" s="44"/>
-      <c r="S36" s="44"/>
-      <c r="T36" s="44"/>
-      <c r="U36" s="44"/>
-      <c r="V36" s="44"/>
-      <c r="W36" s="44"/>
-      <c r="X36" s="44"/>
-      <c r="Y36" s="44"/>
-      <c r="Z36" s="44"/>
-      <c r="AA36" s="44"/>
-      <c r="AB36" s="44"/>
-      <c r="AC36" s="44"/>
+      <c r="F36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB36" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC36" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD36" s="44"/>
       <c r="AE36" s="44"/>
       <c r="AF36" s="44"/>
@@ -7608,30 +9288,78 @@
       <c r="E37" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="44"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
-      <c r="R37" s="44"/>
-      <c r="S37" s="44"/>
-      <c r="T37" s="44"/>
-      <c r="U37" s="44"/>
-      <c r="V37" s="44"/>
-      <c r="W37" s="44"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="44"/>
-      <c r="Z37" s="44"/>
-      <c r="AA37" s="44"/>
-      <c r="AB37" s="44"/>
-      <c r="AC37" s="44"/>
+      <c r="F37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB37" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC37" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD37" s="44"/>
       <c r="AE37" s="44"/>
       <c r="AF37" s="44"/>
@@ -7687,30 +9415,78 @@
       <c r="E38" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="44"/>
-      <c r="K38" s="44"/>
-      <c r="L38" s="44"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="44"/>
-      <c r="R38" s="44"/>
-      <c r="S38" s="44"/>
-      <c r="T38" s="44"/>
-      <c r="U38" s="44"/>
-      <c r="V38" s="44"/>
-      <c r="W38" s="44"/>
-      <c r="X38" s="44"/>
-      <c r="Y38" s="44"/>
-      <c r="Z38" s="44"/>
-      <c r="AA38" s="44"/>
-      <c r="AB38" s="44"/>
-      <c r="AC38" s="44"/>
+      <c r="F38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB38" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC38" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD38" s="44"/>
       <c r="AE38" s="44"/>
       <c r="AF38" s="44"/>
@@ -7768,30 +9544,78 @@
       <c r="E39" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44"/>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44"/>
-      <c r="P39" s="44"/>
-      <c r="Q39" s="44"/>
-      <c r="R39" s="44"/>
-      <c r="S39" s="44"/>
-      <c r="T39" s="44"/>
-      <c r="U39" s="44"/>
-      <c r="V39" s="44"/>
-      <c r="W39" s="44"/>
-      <c r="X39" s="44"/>
-      <c r="Y39" s="44"/>
-      <c r="Z39" s="44"/>
-      <c r="AA39" s="44"/>
-      <c r="AB39" s="44"/>
-      <c r="AC39" s="44"/>
+      <c r="F39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB39" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC39" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD39" s="44"/>
       <c r="AE39" s="44"/>
       <c r="AF39" s="44"/>
@@ -7847,30 +9671,78 @@
       <c r="E40" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="44"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="44"/>
-      <c r="X40" s="44"/>
-      <c r="Y40" s="44"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="44"/>
-      <c r="AB40" s="44"/>
-      <c r="AC40" s="44"/>
+      <c r="F40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB40" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC40" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD40" s="44"/>
       <c r="AE40" s="44"/>
       <c r="AF40" s="44"/>
@@ -7926,30 +9798,78 @@
       <c r="E41" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="44"/>
-      <c r="L41" s="44"/>
-      <c r="M41" s="44"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="44"/>
-      <c r="V41" s="44"/>
-      <c r="W41" s="44"/>
-      <c r="X41" s="44"/>
-      <c r="Y41" s="44"/>
-      <c r="Z41" s="44"/>
-      <c r="AA41" s="44"/>
-      <c r="AB41" s="44"/>
-      <c r="AC41" s="44"/>
+      <c r="F41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB41" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC41" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD41" s="44"/>
       <c r="AE41" s="44"/>
       <c r="AF41" s="44"/>
@@ -8005,30 +9925,78 @@
       <c r="E42" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="44"/>
-      <c r="L42" s="44"/>
-      <c r="M42" s="44"/>
-      <c r="N42" s="44"/>
-      <c r="O42" s="44"/>
-      <c r="P42" s="44"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="44"/>
-      <c r="S42" s="44"/>
-      <c r="T42" s="44"/>
-      <c r="U42" s="44"/>
-      <c r="V42" s="44"/>
-      <c r="W42" s="44"/>
-      <c r="X42" s="44"/>
-      <c r="Y42" s="44"/>
-      <c r="Z42" s="44"/>
-      <c r="AA42" s="44"/>
-      <c r="AB42" s="44"/>
-      <c r="AC42" s="44"/>
+      <c r="F42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB42" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC42" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD42" s="44"/>
       <c r="AE42" s="44"/>
       <c r="AF42" s="44"/>
@@ -8084,30 +10052,78 @@
       <c r="E43" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
-      <c r="L43" s="44"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="44"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="44"/>
-      <c r="U43" s="44"/>
-      <c r="V43" s="44"/>
-      <c r="W43" s="44"/>
-      <c r="X43" s="44"/>
-      <c r="Y43" s="44"/>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="44"/>
-      <c r="AB43" s="44"/>
-      <c r="AC43" s="44"/>
+      <c r="F43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB43" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC43" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD43" s="44"/>
       <c r="AE43" s="44"/>
       <c r="AF43" s="44"/>
@@ -8163,30 +10179,78 @@
       <c r="E44" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="44"/>
-      <c r="L44" s="44"/>
-      <c r="M44" s="44"/>
-      <c r="N44" s="44"/>
-      <c r="O44" s="44"/>
-      <c r="P44" s="44"/>
-      <c r="Q44" s="44"/>
-      <c r="R44" s="44"/>
-      <c r="S44" s="44"/>
-      <c r="T44" s="44"/>
-      <c r="U44" s="44"/>
-      <c r="V44" s="44"/>
-      <c r="W44" s="44"/>
-      <c r="X44" s="44"/>
-      <c r="Y44" s="44"/>
-      <c r="Z44" s="44"/>
-      <c r="AA44" s="44"/>
-      <c r="AB44" s="44"/>
-      <c r="AC44" s="44"/>
+      <c r="F44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB44" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC44" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD44" s="44"/>
       <c r="AE44" s="44"/>
       <c r="AF44" s="44"/>
@@ -8236,30 +10300,78 @@
       <c r="E45" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="44"/>
-      <c r="L45" s="44"/>
-      <c r="M45" s="44"/>
-      <c r="N45" s="44"/>
-      <c r="O45" s="44"/>
-      <c r="P45" s="44"/>
-      <c r="Q45" s="44"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="44"/>
-      <c r="T45" s="44"/>
-      <c r="U45" s="44"/>
-      <c r="V45" s="44"/>
-      <c r="W45" s="44"/>
-      <c r="X45" s="44"/>
-      <c r="Y45" s="44"/>
-      <c r="Z45" s="44"/>
-      <c r="AA45" s="44"/>
-      <c r="AB45" s="44"/>
-      <c r="AC45" s="44"/>
+      <c r="F45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB45" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC45" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD45" s="44"/>
       <c r="AE45" s="44"/>
       <c r="AF45" s="44"/>
@@ -8306,30 +10418,78 @@
       <c r="E46" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="44"/>
-      <c r="O46" s="44"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
-      <c r="R46" s="44"/>
-      <c r="S46" s="44"/>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
-      <c r="V46" s="44"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
-      <c r="Y46" s="44"/>
-      <c r="Z46" s="44"/>
-      <c r="AA46" s="44"/>
-      <c r="AB46" s="44"/>
-      <c r="AC46" s="44"/>
+      <c r="F46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB46" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC46" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD46" s="44"/>
       <c r="AE46" s="44"/>
       <c r="AF46" s="44"/>
@@ -8376,30 +10536,78 @@
       <c r="E47" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="44"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="44"/>
-      <c r="W47" s="44"/>
-      <c r="X47" s="44"/>
-      <c r="Y47" s="44"/>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="44"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="44"/>
+      <c r="F47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB47" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC47" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD47" s="44"/>
       <c r="AE47" s="44"/>
       <c r="AF47" s="44"/>
@@ -8446,30 +10654,78 @@
       <c r="E48" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="44"/>
-      <c r="S48" s="44"/>
-      <c r="T48" s="44"/>
-      <c r="U48" s="44"/>
-      <c r="V48" s="44"/>
-      <c r="W48" s="44"/>
-      <c r="X48" s="44"/>
-      <c r="Y48" s="44"/>
-      <c r="Z48" s="44"/>
-      <c r="AA48" s="44"/>
-      <c r="AB48" s="44"/>
-      <c r="AC48" s="44"/>
+      <c r="F48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB48" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC48" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD48" s="44"/>
       <c r="AE48" s="44"/>
       <c r="AF48" s="44"/>
@@ -8516,30 +10772,78 @@
       <c r="E49" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="44"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="44"/>
-      <c r="L49" s="44"/>
-      <c r="M49" s="44"/>
-      <c r="N49" s="44"/>
-      <c r="O49" s="44"/>
-      <c r="P49" s="44"/>
-      <c r="Q49" s="44"/>
-      <c r="R49" s="44"/>
-      <c r="S49" s="44"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="44"/>
-      <c r="V49" s="44"/>
-      <c r="W49" s="44"/>
-      <c r="X49" s="44"/>
-      <c r="Y49" s="44"/>
-      <c r="Z49" s="44"/>
-      <c r="AA49" s="44"/>
-      <c r="AB49" s="44"/>
-      <c r="AC49" s="44"/>
+      <c r="F49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB49" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC49" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD49" s="44"/>
       <c r="AE49" s="44"/>
       <c r="AF49" s="44"/>
@@ -8586,30 +10890,78 @@
       <c r="E50" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="44"/>
-      <c r="N50" s="44"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44"/>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="44"/>
-      <c r="V50" s="44"/>
-      <c r="W50" s="44"/>
-      <c r="X50" s="44"/>
-      <c r="Y50" s="44"/>
-      <c r="Z50" s="44"/>
-      <c r="AA50" s="44"/>
-      <c r="AB50" s="44"/>
-      <c r="AC50" s="44"/>
+      <c r="F50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB50" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC50" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD50" s="44"/>
       <c r="AE50" s="44"/>
       <c r="AF50" s="44"/>
@@ -8658,30 +11010,78 @@
       <c r="E51" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F51" s="44"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="44"/>
-      <c r="I51" s="44"/>
-      <c r="J51" s="44"/>
-      <c r="K51" s="44"/>
-      <c r="L51" s="44"/>
-      <c r="M51" s="44"/>
-      <c r="N51" s="44"/>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="44"/>
-      <c r="S51" s="44"/>
-      <c r="T51" s="44"/>
-      <c r="U51" s="44"/>
-      <c r="V51" s="44"/>
-      <c r="W51" s="44"/>
-      <c r="X51" s="44"/>
-      <c r="Y51" s="44"/>
-      <c r="Z51" s="44"/>
-      <c r="AA51" s="44"/>
-      <c r="AB51" s="44"/>
-      <c r="AC51" s="44"/>
+      <c r="F51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB51" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC51" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD51" s="44"/>
       <c r="AE51" s="44"/>
       <c r="AF51" s="44"/>
@@ -8730,30 +11130,78 @@
       <c r="E52" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="44"/>
-      <c r="L52" s="44"/>
-      <c r="M52" s="44"/>
-      <c r="N52" s="44"/>
-      <c r="O52" s="44"/>
-      <c r="P52" s="44"/>
-      <c r="Q52" s="44"/>
-      <c r="R52" s="44"/>
-      <c r="S52" s="44"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="44"/>
-      <c r="V52" s="44"/>
-      <c r="W52" s="44"/>
-      <c r="X52" s="44"/>
-      <c r="Y52" s="44"/>
-      <c r="Z52" s="44"/>
-      <c r="AA52" s="44"/>
-      <c r="AB52" s="44"/>
-      <c r="AC52" s="44"/>
+      <c r="F52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="I52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="K52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="O52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="P52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="R52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="U52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="V52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="W52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="X52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB52" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC52" s="44" t="s">
+        <v>104</v>
+      </c>
       <c r="AD52" s="44"/>
       <c r="AE52" s="44"/>
       <c r="AF52" s="44"/>
@@ -8792,7 +11240,7 @@
   </sheetData>
   <autoFilter ref="BI1:BJ44" xr:uid="{760E9C2D-868A-418F-9F2D-C2B8E259D30D}"/>
   <conditionalFormatting sqref="BE2:BG52">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8823,7 +11271,7 @@
     <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
     <col min="14" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" bestFit="1" customWidth="1"/>
@@ -9070,11 +11518,11 @@
       </c>
       <c r="K2" s="8">
         <f>SUM(M7:AC7)</f>
-        <v>51</v>
-      </c>
-      <c r="L2" s="8">
+        <v>867</v>
+      </c>
+      <c r="L2" s="45">
         <f>AVERAGE(M2:AJ2)</f>
-        <v>7.3275862068965511E-2</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="M2" s="8">
         <f t="shared" ref="M2:AR2" si="0">M7/$F$2</f>
@@ -9082,99 +11530,99 @@
       </c>
       <c r="N2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="O2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="P2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="Q2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="R2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="S2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="T2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="U2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="V2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="W2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="X2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="Y2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="Z2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AA2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AB2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AC2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AD2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AE2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AF2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AG2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AH2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AI2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AJ2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7586206896551724</v>
       </c>
       <c r="AK2" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.6896551724137931</v>
       </c>
       <c r="AL2" s="8">
         <f t="shared" si="0"/>
@@ -9568,99 +12016,99 @@
       </c>
       <c r="N7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!F2:F67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!G2:G67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!H2:H67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!I2:I67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!J2:J67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!K2:K67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!L2:L67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="U7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!M2:M67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!N2:N67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="W7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!O2:O67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="X7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!P2:P67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Y7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Q2:Q67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Z7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!R2:R67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AA7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!S2:S67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AB7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!T2:T67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AC7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!U2:U67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AD7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!V2:V67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AE7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!W2:W67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AF7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!X2:X67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AG7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Y2:Y67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AH7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!Z2:Z67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AI7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AA2:AA67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AJ7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AB2:AB67)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AK7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AC2:AC67)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AL7" s="14">
         <f>COUNTA(StatusReport_2026_NovaFormula!AD2:AD67)</f>
@@ -10069,11 +12517,11 @@
       </c>
       <c r="BF2" s="18">
         <f ca="1">WEEKNUM(TODAY())-BE2</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG2">
         <f ca="1">BF2+BE2</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH2"/>
       <c r="BI2" t="s">
@@ -10234,11 +12682,11 @@
       </c>
       <c r="BF4" s="18">
         <f t="shared" ref="BF4:BF43" ca="1" si="1">WEEKNUM(TODAY())-BE4</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG4">
         <f t="shared" ref="BG4:BG43" ca="1" si="2">BF4+BE4</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH4"/>
       <c r="BI4" t="s">
@@ -10331,11 +12779,11 @@
       </c>
       <c r="BF5" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG5">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH5"/>
       <c r="BI5" t="s">
@@ -10416,11 +12864,11 @@
       </c>
       <c r="BF6" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG6">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH6"/>
       <c r="BI6" t="s">
@@ -10501,11 +12949,11 @@
       </c>
       <c r="BF7" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG7">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH7"/>
       <c r="BI7" t="s">
@@ -10583,11 +13031,11 @@
       </c>
       <c r="BF8" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG8">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH8"/>
       <c r="BI8" t="s">
@@ -10665,11 +13113,11 @@
       </c>
       <c r="BF9" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG9">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH9"/>
       <c r="BI9" t="s">
@@ -10747,11 +13195,11 @@
       </c>
       <c r="BF10" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG10">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH10"/>
       <c r="BI10" t="s">
@@ -10845,11 +13293,11 @@
       </c>
       <c r="BF11" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG11">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH11"/>
       <c r="BI11" t="s">
@@ -10930,11 +13378,11 @@
       </c>
       <c r="BF12" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG12">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH12"/>
       <c r="BI12" t="s">
@@ -11036,11 +13484,11 @@
       </c>
       <c r="BF13" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG13">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH13"/>
       <c r="BI13" t="s">
@@ -11130,11 +13578,11 @@
       </c>
       <c r="BF14" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG14">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH14"/>
       <c r="BI14" t="s">
@@ -11212,11 +13660,11 @@
       </c>
       <c r="BF15" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG15">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH15"/>
       <c r="BI15" t="s">
@@ -11306,11 +13754,11 @@
       </c>
       <c r="BF16" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG16">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH16"/>
       <c r="BI16" t="s">
@@ -11391,11 +13839,11 @@
       </c>
       <c r="BF17" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG17">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH17"/>
       <c r="BI17" t="s">
@@ -11515,11 +13963,11 @@
       </c>
       <c r="BF18" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG18">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH18"/>
       <c r="BI18" t="s">
@@ -11607,11 +14055,11 @@
       </c>
       <c r="BF19" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG19">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH19"/>
       <c r="BI19" t="s">
@@ -11692,11 +14140,11 @@
       </c>
       <c r="BF20" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG20">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH20"/>
       <c r="BI20" t="s">
@@ -11778,11 +14226,11 @@
       </c>
       <c r="BF21" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG21">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH21"/>
       <c r="BI21" t="s">
@@ -11861,11 +14309,11 @@
       </c>
       <c r="BF22" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG22">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH22"/>
       <c r="BI22" t="s">
@@ -11947,11 +14395,11 @@
       </c>
       <c r="BF23" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG23">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH23"/>
       <c r="BI23" t="s">
@@ -12029,11 +14477,11 @@
       </c>
       <c r="BF24" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG24">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH24"/>
       <c r="BI24" t="s">
@@ -12111,11 +14559,11 @@
       </c>
       <c r="BF25" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG25">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH25"/>
       <c r="BI25" t="s">
@@ -12216,11 +14664,11 @@
       </c>
       <c r="BF26" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG26">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH26"/>
       <c r="BI26" t="s">
@@ -12319,11 +14767,11 @@
       </c>
       <c r="BF27" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG27">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH27"/>
       <c r="BI27" t="s">
@@ -12424,11 +14872,11 @@
       </c>
       <c r="BF28" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG28">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH28"/>
       <c r="BI28" t="s">
@@ -12529,11 +14977,11 @@
       </c>
       <c r="BF29" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG29">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH29"/>
       <c r="BI29" t="s">
@@ -12625,7 +15073,7 @@
       <c r="BE30" s="4"/>
       <c r="BF30" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG30"/>
       <c r="BH30"/>
@@ -12731,11 +15179,11 @@
       </c>
       <c r="BF31" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG31">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH31"/>
       <c r="BI31" t="s">
@@ -12813,11 +15261,11 @@
       </c>
       <c r="BF32" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG32">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH32"/>
       <c r="BI32" t="s">
@@ -12908,11 +15356,11 @@
       </c>
       <c r="BF33" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="BG33">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH33"/>
       <c r="BI33" t="s">
@@ -13003,11 +15451,11 @@
       </c>
       <c r="BF34" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG34">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH34"/>
       <c r="BI34" t="s">
@@ -13098,11 +15546,11 @@
       </c>
       <c r="BF35" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG35">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH35"/>
       <c r="BI35" t="s">
@@ -13207,11 +15655,11 @@
       </c>
       <c r="BF36" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG36">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH36"/>
       <c r="BI36" t="s">
@@ -13294,11 +15742,11 @@
       </c>
       <c r="BF37" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG37">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH37"/>
       <c r="BI37" t="s">
@@ -13376,11 +15824,11 @@
       </c>
       <c r="BF38" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG38">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH38"/>
       <c r="BI38" t="s">
@@ -13459,11 +15907,11 @@
       </c>
       <c r="BF39" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG39">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH39"/>
       <c r="BI39" t="s">
@@ -13552,11 +16000,11 @@
       </c>
       <c r="BF40" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG40">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH40"/>
       <c r="BI40" t="s">
@@ -13647,11 +16095,11 @@
       </c>
       <c r="BF41" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG41">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH41"/>
       <c r="BI41" t="s">
@@ -13732,11 +16180,11 @@
       </c>
       <c r="BF42" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG42">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH42"/>
       <c r="BI42" t="s">
@@ -13817,11 +16265,11 @@
       </c>
       <c r="BF43" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG43">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH43"/>
       <c r="BI43" t="s">
@@ -13836,12 +16284,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C20">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE2:BG43">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13858,29 +16306,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9e324e9-4967-437b-a497-16f662c21391">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="dcbe9599-1178-413b-9602-83ebc6e8bce4" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DocumentCategory xmlns="e7640078-2807-4792-8712-763d4cb58983" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D45F55DA03AD8849999218AD871CBDF0" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3a836707be849dfa7ce4683be2486502">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="e7640078-2807-4792-8712-763d4cb58983" xmlns:ns3="dcbe9599-1178-413b-9602-83ebc6e8bce4" xmlns:ns4="e9e324e9-4967-437b-a497-16f662c21391" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f940417f33b8f1f2ce4246c9e35d0ae" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -14153,32 +16578,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9e324e9-4967-437b-a497-16f662c21391">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="dcbe9599-1178-413b-9602-83ebc6e8bce4" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DocumentCategory xmlns="e7640078-2807-4792-8712-763d4cb58983" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A07560-16E1-4559-8CE1-6DDA79DFE9DD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="e9e324e9-4967-437b-a497-16f662c21391"/>
-    <ds:schemaRef ds:uri="dcbe9599-1178-413b-9602-83ebc6e8bce4"/>
-    <ds:schemaRef ds:uri="e7640078-2807-4792-8712-763d4cb58983"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BA007C-FCAF-45A2-BE18-B36EE22CEF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65533DC7-38B6-47C2-9AFD-406A18AF675D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14199,6 +16626,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BA007C-FCAF-45A2-BE18-B36EE22CEF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A07560-16E1-4559-8CE1-6DDA79DFE9DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="e9e324e9-4967-437b-a497-16f662c21391"/>
+    <ds:schemaRef ds:uri="dcbe9599-1178-413b-9602-83ebc6e8bce4"/>
+    <ds:schemaRef ds:uri="e7640078-2807-4792-8712-763d4cb58983"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D875DB42-104D-4A36-925C-E0DD5B997017}">
   <ds:schemaRefs>
